--- a/filer/32345794_apm.xlsx
+++ b/filer/32345794_apm.xlsx
@@ -202,8 +202,8 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="3" fillId="4" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="3" fillId="4" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="2" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="4" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -628,7 +628,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L84"/>
+  <dimension ref="A1:L87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="54" customWidth="1" min="1" max="1"/>
@@ -1659,241 +1659,241 @@
       </c>
     </row>
     <row r="25" ht="16" customHeight="1">
-      <c r="A25" s="10" t="inlineStr">
+      <c r="A25" s="7" t="inlineStr">
+        <is>
+          <t>Kapitalandele, dattervirksomheder</t>
+        </is>
+      </c>
+      <c r="B25" s="8">
+        <f>'balance_raw'!$B$4</f>
+        <v/>
+      </c>
+      <c r="C25" s="8">
+        <f>'balance_raw'!$C$4</f>
+        <v/>
+      </c>
+      <c r="D25" s="8">
+        <f>'balance_raw'!$D$4</f>
+        <v/>
+      </c>
+      <c r="E25" s="8">
+        <f>'balance_raw'!$E$4</f>
+        <v/>
+      </c>
+      <c r="F25" s="8">
+        <f>'balance_raw'!$F$4</f>
+        <v/>
+      </c>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" s="9">
+        <f>IFERROR(B25/$B$25*100,"")</f>
+        <v/>
+      </c>
+      <c r="I25" s="9">
+        <f>IFERROR(C25/$B$25*100,"")</f>
+        <v/>
+      </c>
+      <c r="J25" s="9">
+        <f>IFERROR(D25/$B$25*100,"")</f>
+        <v/>
+      </c>
+      <c r="K25" s="9">
+        <f>IFERROR(E25/$B$25*100,"")</f>
+        <v/>
+      </c>
+      <c r="L25" s="9">
+        <f>IFERROR(F25/$B$25*100,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26" ht="16" customHeight="1">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>Deposita</t>
+        </is>
+      </c>
+      <c r="B26" s="5">
+        <f>'balance_raw'!$B$5</f>
+        <v/>
+      </c>
+      <c r="C26" s="5">
+        <f>'balance_raw'!$C$5</f>
+        <v/>
+      </c>
+      <c r="D26" s="5">
+        <f>'balance_raw'!$D$5</f>
+        <v/>
+      </c>
+      <c r="E26" s="5">
+        <f>'balance_raw'!$E$5</f>
+        <v/>
+      </c>
+      <c r="F26" s="5">
+        <f>'balance_raw'!$F$5</f>
+        <v/>
+      </c>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" s="6">
+        <f>IFERROR(B26/$B$26*100,"")</f>
+        <v/>
+      </c>
+      <c r="I26" s="6">
+        <f>IFERROR(C26/$B$26*100,"")</f>
+        <v/>
+      </c>
+      <c r="J26" s="6">
+        <f>IFERROR(D26/$B$26*100,"")</f>
+        <v/>
+      </c>
+      <c r="K26" s="6">
+        <f>IFERROR(E26/$B$26*100,"")</f>
+        <v/>
+      </c>
+      <c r="L26" s="6">
+        <f>IFERROR(F26/$B$26*100,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27" ht="16" customHeight="1">
+      <c r="A27" s="10" t="inlineStr">
+        <is>
+          <t>Finansielle anlægsaktiver</t>
+        </is>
+      </c>
+      <c r="B27" s="11">
+        <f>'balance_raw'!$B$6</f>
+        <v/>
+      </c>
+      <c r="C27" s="11">
+        <f>'balance_raw'!$C$6</f>
+        <v/>
+      </c>
+      <c r="D27" s="11">
+        <f>'balance_raw'!$D$6</f>
+        <v/>
+      </c>
+      <c r="E27" s="11">
+        <f>'balance_raw'!$E$6</f>
+        <v/>
+      </c>
+      <c r="F27" s="11">
+        <f>'balance_raw'!$F$6</f>
+        <v/>
+      </c>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" s="12">
+        <f>IFERROR(B27/$B$27*100,"")</f>
+        <v/>
+      </c>
+      <c r="I27" s="12">
+        <f>IFERROR(C27/$B$27*100,"")</f>
+        <v/>
+      </c>
+      <c r="J27" s="12">
+        <f>IFERROR(D27/$B$27*100,"")</f>
+        <v/>
+      </c>
+      <c r="K27" s="12">
+        <f>IFERROR(E27/$B$27*100,"")</f>
+        <v/>
+      </c>
+      <c r="L27" s="12">
+        <f>IFERROR(F27/$B$27*100,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28" ht="16" customHeight="1">
+      <c r="A28" s="10" t="inlineStr">
         <is>
           <t>Anlægsaktiver</t>
         </is>
       </c>
-      <c r="B25" s="11">
-        <f>'balance_raw'!$B$4</f>
-        <v/>
-      </c>
-      <c r="C25" s="11">
-        <f>'balance_raw'!$C$4</f>
-        <v/>
-      </c>
-      <c r="D25" s="11">
-        <f>'balance_raw'!$D$4</f>
-        <v/>
-      </c>
-      <c r="E25" s="11">
-        <f>'balance_raw'!$E$4</f>
-        <v/>
-      </c>
-      <c r="F25" s="11">
-        <f>'balance_raw'!$F$4</f>
-        <v/>
-      </c>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" s="12">
-        <f>IFERROR(B25/$B$25*100,"")</f>
-        <v/>
-      </c>
-      <c r="I25" s="12">
-        <f>IFERROR(C25/$B$25*100,"")</f>
-        <v/>
-      </c>
-      <c r="J25" s="12">
-        <f>IFERROR(D25/$B$25*100,"")</f>
-        <v/>
-      </c>
-      <c r="K25" s="12">
-        <f>IFERROR(E25/$B$25*100,"")</f>
-        <v/>
-      </c>
-      <c r="L25" s="12">
-        <f>IFERROR(F25/$B$25*100,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="26" ht="16" customHeight="1">
-      <c r="A26" s="10" t="inlineStr">
+      <c r="B28" s="11">
+        <f>'balance_raw'!$B$7</f>
+        <v/>
+      </c>
+      <c r="C28" s="11">
+        <f>'balance_raw'!$C$7</f>
+        <v/>
+      </c>
+      <c r="D28" s="11">
+        <f>'balance_raw'!$D$7</f>
+        <v/>
+      </c>
+      <c r="E28" s="11">
+        <f>'balance_raw'!$E$7</f>
+        <v/>
+      </c>
+      <c r="F28" s="11">
+        <f>'balance_raw'!$F$7</f>
+        <v/>
+      </c>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" s="12">
+        <f>IFERROR(B28/$B$28*100,"")</f>
+        <v/>
+      </c>
+      <c r="I28" s="12">
+        <f>IFERROR(C28/$B$28*100,"")</f>
+        <v/>
+      </c>
+      <c r="J28" s="12">
+        <f>IFERROR(D28/$B$28*100,"")</f>
+        <v/>
+      </c>
+      <c r="K28" s="12">
+        <f>IFERROR(E28/$B$28*100,"")</f>
+        <v/>
+      </c>
+      <c r="L28" s="12">
+        <f>IFERROR(F28/$B$28*100,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29" ht="16" customHeight="1">
+      <c r="A29" s="10" t="inlineStr">
         <is>
           <t>Varebeholdninger</t>
         </is>
       </c>
-      <c r="B26" s="11">
-        <f>'balance_raw'!$B$5</f>
-        <v/>
-      </c>
-      <c r="C26" s="11">
-        <f>'balance_raw'!$C$5</f>
-        <v/>
-      </c>
-      <c r="D26" s="11">
-        <f>'balance_raw'!$D$5</f>
-        <v/>
-      </c>
-      <c r="E26" s="11">
-        <f>'balance_raw'!$E$5</f>
-        <v/>
-      </c>
-      <c r="F26" s="11">
-        <f>'balance_raw'!$F$5</f>
-        <v/>
-      </c>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" s="12">
-        <f>IFERROR(B26/$B$26*100,"")</f>
-        <v/>
-      </c>
-      <c r="I26" s="12">
-        <f>IFERROR(C26/$B$26*100,"")</f>
-        <v/>
-      </c>
-      <c r="J26" s="12">
-        <f>IFERROR(D26/$B$26*100,"")</f>
-        <v/>
-      </c>
-      <c r="K26" s="12">
-        <f>IFERROR(E26/$B$26*100,"")</f>
-        <v/>
-      </c>
-      <c r="L26" s="12">
-        <f>IFERROR(F26/$B$26*100,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="27" ht="16" customHeight="1">
-      <c r="A27" s="7" t="inlineStr">
-        <is>
-          <t>Tilgodehavender fra salg og tjenesteydelser</t>
-        </is>
-      </c>
-      <c r="B27" s="8">
-        <f>'balance_raw'!$B$6</f>
-        <v/>
-      </c>
-      <c r="C27" s="8">
-        <f>'balance_raw'!$C$6</f>
-        <v/>
-      </c>
-      <c r="D27" s="8">
-        <f>'balance_raw'!$D$6</f>
-        <v/>
-      </c>
-      <c r="E27" s="8">
-        <f>'balance_raw'!$E$6</f>
-        <v/>
-      </c>
-      <c r="F27" s="8">
-        <f>'balance_raw'!$F$6</f>
-        <v/>
-      </c>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" s="9">
-        <f>IFERROR(B27/$B$27*100,"")</f>
-        <v/>
-      </c>
-      <c r="I27" s="9">
-        <f>IFERROR(C27/$B$27*100,"")</f>
-        <v/>
-      </c>
-      <c r="J27" s="9">
-        <f>IFERROR(D27/$B$27*100,"")</f>
-        <v/>
-      </c>
-      <c r="K27" s="9">
-        <f>IFERROR(E27/$B$27*100,"")</f>
-        <v/>
-      </c>
-      <c r="L27" s="9">
-        <f>IFERROR(F27/$B$27*100,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="28" ht="16" customHeight="1">
-      <c r="A28" s="4" t="inlineStr">
-        <is>
-          <t>Tilgodehavender hos tilknyttede virksomheder</t>
-        </is>
-      </c>
-      <c r="B28" s="5">
-        <f>'balance_raw'!$B$7</f>
-        <v/>
-      </c>
-      <c r="C28" s="5">
-        <f>'balance_raw'!$C$7</f>
-        <v/>
-      </c>
-      <c r="D28" s="5">
-        <f>'balance_raw'!$D$7</f>
-        <v/>
-      </c>
-      <c r="E28" s="5">
-        <f>'balance_raw'!$E$7</f>
-        <v/>
-      </c>
-      <c r="F28" s="5">
-        <f>'balance_raw'!$F$7</f>
-        <v/>
-      </c>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" s="6">
-        <f>IFERROR(B28/$B$28*100,"")</f>
-        <v/>
-      </c>
-      <c r="I28" s="6">
-        <f>IFERROR(C28/$B$28*100,"")</f>
-        <v/>
-      </c>
-      <c r="J28" s="6">
-        <f>IFERROR(D28/$B$28*100,"")</f>
-        <v/>
-      </c>
-      <c r="K28" s="6">
-        <f>IFERROR(E28/$B$28*100,"")</f>
-        <v/>
-      </c>
-      <c r="L28" s="6">
-        <f>IFERROR(F28/$B$28*100,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="29" ht="16" customHeight="1">
-      <c r="A29" s="7" t="inlineStr">
-        <is>
-          <t>Andre tilgodehavender</t>
-        </is>
-      </c>
-      <c r="B29" s="8">
+      <c r="B29" s="11">
         <f>'balance_raw'!$B$8</f>
         <v/>
       </c>
-      <c r="C29" s="8">
+      <c r="C29" s="11">
         <f>'balance_raw'!$C$8</f>
         <v/>
       </c>
-      <c r="D29" s="8">
+      <c r="D29" s="11">
         <f>'balance_raw'!$D$8</f>
         <v/>
       </c>
-      <c r="E29" s="8">
+      <c r="E29" s="11">
         <f>'balance_raw'!$E$8</f>
         <v/>
       </c>
-      <c r="F29" s="8">
+      <c r="F29" s="11">
         <f>'balance_raw'!$F$8</f>
         <v/>
       </c>
       <c r="G29" t="inlineStr"/>
-      <c r="H29" s="9">
+      <c r="H29" s="12">
         <f>IFERROR(B29/$B$29*100,"")</f>
         <v/>
       </c>
-      <c r="I29" s="9">
+      <c r="I29" s="12">
         <f>IFERROR(C29/$B$29*100,"")</f>
         <v/>
       </c>
-      <c r="J29" s="9">
+      <c r="J29" s="12">
         <f>IFERROR(D29/$B$29*100,"")</f>
         <v/>
       </c>
-      <c r="K29" s="9">
+      <c r="K29" s="12">
         <f>IFERROR(E29/$B$29*100,"")</f>
         <v/>
       </c>
-      <c r="L29" s="9">
+      <c r="L29" s="12">
         <f>IFERROR(F29/$B$29*100,"")</f>
         <v/>
       </c>
@@ -1901,7 +1901,7 @@
     <row r="30" ht="16" customHeight="1">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>Periodeafgrænsningsposter (aktiver)</t>
+          <t>Tilgodehavender fra salg og tjenesteydelser</t>
         </is>
       </c>
       <c r="B30" s="5">
@@ -1949,7 +1949,7 @@
     <row r="31" ht="16" customHeight="1">
       <c r="A31" s="7" t="inlineStr">
         <is>
-          <t>Udskudt skatteaktiv</t>
+          <t>Tilgodehavender hos tilknyttede virksomheder</t>
         </is>
       </c>
       <c r="B31" s="8">
@@ -1997,7 +1997,7 @@
     <row r="32" ht="16" customHeight="1">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>Tilgodehavende skat hos tilknyttede virksomheder</t>
+          <t>Andre tilgodehavender</t>
         </is>
       </c>
       <c r="B32" s="5">
@@ -2045,7 +2045,7 @@
     <row r="33" ht="16" customHeight="1">
       <c r="A33" s="7" t="inlineStr">
         <is>
-          <t>Kortfristede skattetilgodehavender</t>
+          <t>Periodeafgrænsningsposter (aktiver)</t>
         </is>
       </c>
       <c r="B33" s="8">
@@ -2091,49 +2091,49 @@
       </c>
     </row>
     <row r="34" ht="16" customHeight="1">
-      <c r="A34" s="10" t="inlineStr">
-        <is>
-          <t>Tilgodehavender</t>
-        </is>
-      </c>
-      <c r="B34" s="11">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>Udskudt skatteaktiv</t>
+        </is>
+      </c>
+      <c r="B34" s="5">
         <f>'balance_raw'!$B$13</f>
         <v/>
       </c>
-      <c r="C34" s="11">
+      <c r="C34" s="5">
         <f>'balance_raw'!$C$13</f>
         <v/>
       </c>
-      <c r="D34" s="11">
+      <c r="D34" s="5">
         <f>'balance_raw'!$D$13</f>
         <v/>
       </c>
-      <c r="E34" s="11">
+      <c r="E34" s="5">
         <f>'balance_raw'!$E$13</f>
         <v/>
       </c>
-      <c r="F34" s="11">
+      <c r="F34" s="5">
         <f>'balance_raw'!$F$13</f>
         <v/>
       </c>
       <c r="G34" t="inlineStr"/>
-      <c r="H34" s="12">
+      <c r="H34" s="6">
         <f>IFERROR(B34/$B$34*100,"")</f>
         <v/>
       </c>
-      <c r="I34" s="12">
+      <c r="I34" s="6">
         <f>IFERROR(C34/$B$34*100,"")</f>
         <v/>
       </c>
-      <c r="J34" s="12">
+      <c r="J34" s="6">
         <f>IFERROR(D34/$B$34*100,"")</f>
         <v/>
       </c>
-      <c r="K34" s="12">
+      <c r="K34" s="6">
         <f>IFERROR(E34/$B$34*100,"")</f>
         <v/>
       </c>
-      <c r="L34" s="12">
+      <c r="L34" s="6">
         <f>IFERROR(F34/$B$34*100,"")</f>
         <v/>
       </c>
@@ -2141,7 +2141,7 @@
     <row r="35" ht="16" customHeight="1">
       <c r="A35" s="7" t="inlineStr">
         <is>
-          <t>Værdipapirer</t>
+          <t>Tilgodehavende skat hos tilknyttede virksomheder</t>
         </is>
       </c>
       <c r="B35" s="8">
@@ -2189,7 +2189,7 @@
     <row r="36" ht="16" customHeight="1">
       <c r="A36" s="4" t="inlineStr">
         <is>
-          <t>Likvide beholdninger</t>
+          <t>Kortfristede skattetilgodehavender</t>
         </is>
       </c>
       <c r="B36" s="5">
@@ -2237,7 +2237,7 @@
     <row r="37" ht="16" customHeight="1">
       <c r="A37" s="10" t="inlineStr">
         <is>
-          <t>Omsætningsaktiver</t>
+          <t>Tilgodehavender</t>
         </is>
       </c>
       <c r="B37" s="11">
@@ -2283,239 +2283,239 @@
       </c>
     </row>
     <row r="38" ht="16" customHeight="1">
-      <c r="A38" s="10" t="inlineStr">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>Værdipapirer</t>
+        </is>
+      </c>
+      <c r="B38" s="5">
+        <f>'balance_raw'!$B$17</f>
+        <v/>
+      </c>
+      <c r="C38" s="5">
+        <f>'balance_raw'!$C$17</f>
+        <v/>
+      </c>
+      <c r="D38" s="5">
+        <f>'balance_raw'!$D$17</f>
+        <v/>
+      </c>
+      <c r="E38" s="5">
+        <f>'balance_raw'!$E$17</f>
+        <v/>
+      </c>
+      <c r="F38" s="5">
+        <f>'balance_raw'!$F$17</f>
+        <v/>
+      </c>
+      <c r="G38" t="inlineStr"/>
+      <c r="H38" s="6">
+        <f>IFERROR(B38/$B$38*100,"")</f>
+        <v/>
+      </c>
+      <c r="I38" s="6">
+        <f>IFERROR(C38/$B$38*100,"")</f>
+        <v/>
+      </c>
+      <c r="J38" s="6">
+        <f>IFERROR(D38/$B$38*100,"")</f>
+        <v/>
+      </c>
+      <c r="K38" s="6">
+        <f>IFERROR(E38/$B$38*100,"")</f>
+        <v/>
+      </c>
+      <c r="L38" s="6">
+        <f>IFERROR(F38/$B$38*100,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39" ht="16" customHeight="1">
+      <c r="A39" s="7" t="inlineStr">
+        <is>
+          <t>Likvide beholdninger</t>
+        </is>
+      </c>
+      <c r="B39" s="8">
+        <f>'balance_raw'!$B$18</f>
+        <v/>
+      </c>
+      <c r="C39" s="8">
+        <f>'balance_raw'!$C$18</f>
+        <v/>
+      </c>
+      <c r="D39" s="8">
+        <f>'balance_raw'!$D$18</f>
+        <v/>
+      </c>
+      <c r="E39" s="8">
+        <f>'balance_raw'!$E$18</f>
+        <v/>
+      </c>
+      <c r="F39" s="8">
+        <f>'balance_raw'!$F$18</f>
+        <v/>
+      </c>
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" s="9">
+        <f>IFERROR(B39/$B$39*100,"")</f>
+        <v/>
+      </c>
+      <c r="I39" s="9">
+        <f>IFERROR(C39/$B$39*100,"")</f>
+        <v/>
+      </c>
+      <c r="J39" s="9">
+        <f>IFERROR(D39/$B$39*100,"")</f>
+        <v/>
+      </c>
+      <c r="K39" s="9">
+        <f>IFERROR(E39/$B$39*100,"")</f>
+        <v/>
+      </c>
+      <c r="L39" s="9">
+        <f>IFERROR(F39/$B$39*100,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40" ht="16" customHeight="1">
+      <c r="A40" s="10" t="inlineStr">
+        <is>
+          <t>Omsætningsaktiver</t>
+        </is>
+      </c>
+      <c r="B40" s="11">
+        <f>'balance_raw'!$B$19</f>
+        <v/>
+      </c>
+      <c r="C40" s="11">
+        <f>'balance_raw'!$C$19</f>
+        <v/>
+      </c>
+      <c r="D40" s="11">
+        <f>'balance_raw'!$D$19</f>
+        <v/>
+      </c>
+      <c r="E40" s="11">
+        <f>'balance_raw'!$E$19</f>
+        <v/>
+      </c>
+      <c r="F40" s="11">
+        <f>'balance_raw'!$F$19</f>
+        <v/>
+      </c>
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" s="12">
+        <f>IFERROR(B40/$B$40*100,"")</f>
+        <v/>
+      </c>
+      <c r="I40" s="12">
+        <f>IFERROR(C40/$B$40*100,"")</f>
+        <v/>
+      </c>
+      <c r="J40" s="12">
+        <f>IFERROR(D40/$B$40*100,"")</f>
+        <v/>
+      </c>
+      <c r="K40" s="12">
+        <f>IFERROR(E40/$B$40*100,"")</f>
+        <v/>
+      </c>
+      <c r="L40" s="12">
+        <f>IFERROR(F40/$B$40*100,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41" ht="16" customHeight="1">
+      <c r="A41" s="10" t="inlineStr">
         <is>
           <t>Aktiver</t>
         </is>
       </c>
-      <c r="B38" s="11">
-        <f>'balance_raw'!$B$17</f>
-        <v/>
-      </c>
-      <c r="C38" s="11">
-        <f>'balance_raw'!$C$17</f>
-        <v/>
-      </c>
-      <c r="D38" s="11">
-        <f>'balance_raw'!$D$17</f>
-        <v/>
-      </c>
-      <c r="E38" s="11">
-        <f>'balance_raw'!$E$17</f>
-        <v/>
-      </c>
-      <c r="F38" s="11">
-        <f>'balance_raw'!$F$17</f>
-        <v/>
-      </c>
-      <c r="G38" t="inlineStr"/>
-      <c r="H38" s="12">
-        <f>IFERROR(B38/$B$38*100,"")</f>
-        <v/>
-      </c>
-      <c r="I38" s="12">
-        <f>IFERROR(C38/$B$38*100,"")</f>
-        <v/>
-      </c>
-      <c r="J38" s="12">
-        <f>IFERROR(D38/$B$38*100,"")</f>
-        <v/>
-      </c>
-      <c r="K38" s="12">
-        <f>IFERROR(E38/$B$38*100,"")</f>
-        <v/>
-      </c>
-      <c r="L38" s="12">
-        <f>IFERROR(F38/$B$38*100,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="40" ht="22" customHeight="1">
-      <c r="A40" s="3" t="inlineStr">
+      <c r="B41" s="11">
+        <f>'balance_raw'!$B$20</f>
+        <v/>
+      </c>
+      <c r="C41" s="11">
+        <f>'balance_raw'!$C$20</f>
+        <v/>
+      </c>
+      <c r="D41" s="11">
+        <f>'balance_raw'!$D$20</f>
+        <v/>
+      </c>
+      <c r="E41" s="11">
+        <f>'balance_raw'!$E$20</f>
+        <v/>
+      </c>
+      <c r="F41" s="11">
+        <f>'balance_raw'!$F$20</f>
+        <v/>
+      </c>
+      <c r="G41" t="inlineStr"/>
+      <c r="H41" s="12">
+        <f>IFERROR(B41/$B$41*100,"")</f>
+        <v/>
+      </c>
+      <c r="I41" s="12">
+        <f>IFERROR(C41/$B$41*100,"")</f>
+        <v/>
+      </c>
+      <c r="J41" s="12">
+        <f>IFERROR(D41/$B$41*100,"")</f>
+        <v/>
+      </c>
+      <c r="K41" s="12">
+        <f>IFERROR(E41/$B$41*100,"")</f>
+        <v/>
+      </c>
+      <c r="L41" s="12">
+        <f>IFERROR(F41/$B$41*100,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43" ht="22" customHeight="1">
+      <c r="A43" s="3" t="inlineStr">
         <is>
           <t>PASSIVER t.kr.</t>
         </is>
       </c>
-      <c r="B40" s="3" t="n">
+      <c r="B43" s="3" t="n">
         <v>2020</v>
       </c>
-      <c r="C40" s="3" t="n">
+      <c r="C43" s="3" t="n">
         <v>2021</v>
       </c>
-      <c r="D40" s="3" t="n">
+      <c r="D43" s="3" t="n">
         <v>2022</v>
       </c>
-      <c r="E40" s="3" t="n">
+      <c r="E43" s="3" t="n">
         <v>2023</v>
       </c>
-      <c r="F40" s="3" t="n">
+      <c r="F43" s="3" t="n">
         <v>2024</v>
       </c>
-      <c r="G40" t="inlineStr"/>
-      <c r="H40" s="3" t="n">
+      <c r="G43" t="inlineStr"/>
+      <c r="H43" s="3" t="n">
         <v>2020</v>
       </c>
-      <c r="I40" s="3" t="n">
+      <c r="I43" s="3" t="n">
         <v>2021</v>
       </c>
-      <c r="J40" s="3" t="n">
+      <c r="J43" s="3" t="n">
         <v>2022</v>
       </c>
-      <c r="K40" s="3" t="n">
+      <c r="K43" s="3" t="n">
         <v>2023</v>
       </c>
-      <c r="L40" s="3" t="n">
+      <c r="L43" s="3" t="n">
         <v>2024</v>
-      </c>
-    </row>
-    <row r="41" ht="16" customHeight="1">
-      <c r="A41" s="7" t="inlineStr">
-        <is>
-          <t>Selskabskapital</t>
-        </is>
-      </c>
-      <c r="B41" s="8">
-        <f>'balance_raw'!$B$18</f>
-        <v/>
-      </c>
-      <c r="C41" s="8">
-        <f>'balance_raw'!$C$18</f>
-        <v/>
-      </c>
-      <c r="D41" s="8">
-        <f>'balance_raw'!$D$18</f>
-        <v/>
-      </c>
-      <c r="E41" s="8">
-        <f>'balance_raw'!$E$18</f>
-        <v/>
-      </c>
-      <c r="F41" s="8">
-        <f>'balance_raw'!$F$18</f>
-        <v/>
-      </c>
-      <c r="G41" t="inlineStr"/>
-      <c r="H41" s="9">
-        <f>IFERROR(B41/$B$41*100,"")</f>
-        <v/>
-      </c>
-      <c r="I41" s="9">
-        <f>IFERROR(C41/$B$41*100,"")</f>
-        <v/>
-      </c>
-      <c r="J41" s="9">
-        <f>IFERROR(D41/$B$41*100,"")</f>
-        <v/>
-      </c>
-      <c r="K41" s="9">
-        <f>IFERROR(E41/$B$41*100,"")</f>
-        <v/>
-      </c>
-      <c r="L41" s="9">
-        <f>IFERROR(F41/$B$41*100,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="42" ht="16" customHeight="1">
-      <c r="A42" s="4" t="inlineStr">
-        <is>
-          <t>Reserve for nettoopskrivning (indre værdis metode)</t>
-        </is>
-      </c>
-      <c r="B42" s="5">
-        <f>'balance_raw'!$B$19</f>
-        <v/>
-      </c>
-      <c r="C42" s="5">
-        <f>'balance_raw'!$C$19</f>
-        <v/>
-      </c>
-      <c r="D42" s="5">
-        <f>'balance_raw'!$D$19</f>
-        <v/>
-      </c>
-      <c r="E42" s="5">
-        <f>'balance_raw'!$E$19</f>
-        <v/>
-      </c>
-      <c r="F42" s="5">
-        <f>'balance_raw'!$F$19</f>
-        <v/>
-      </c>
-      <c r="G42" t="inlineStr"/>
-      <c r="H42" s="6">
-        <f>IFERROR(B42/$B$42*100,"")</f>
-        <v/>
-      </c>
-      <c r="I42" s="6">
-        <f>IFERROR(C42/$B$42*100,"")</f>
-        <v/>
-      </c>
-      <c r="J42" s="6">
-        <f>IFERROR(D42/$B$42*100,"")</f>
-        <v/>
-      </c>
-      <c r="K42" s="6">
-        <f>IFERROR(E42/$B$42*100,"")</f>
-        <v/>
-      </c>
-      <c r="L42" s="6">
-        <f>IFERROR(F42/$B$42*100,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="43" ht="16" customHeight="1">
-      <c r="A43" s="7" t="inlineStr">
-        <is>
-          <t>Reserve for udviklingsomkostninger</t>
-        </is>
-      </c>
-      <c r="B43" s="8">
-        <f>'balance_raw'!$B$20</f>
-        <v/>
-      </c>
-      <c r="C43" s="8">
-        <f>'balance_raw'!$C$20</f>
-        <v/>
-      </c>
-      <c r="D43" s="8">
-        <f>'balance_raw'!$D$20</f>
-        <v/>
-      </c>
-      <c r="E43" s="8">
-        <f>'balance_raw'!$E$20</f>
-        <v/>
-      </c>
-      <c r="F43" s="8">
-        <f>'balance_raw'!$F$20</f>
-        <v/>
-      </c>
-      <c r="G43" t="inlineStr"/>
-      <c r="H43" s="9">
-        <f>IFERROR(B43/$B$43*100,"")</f>
-        <v/>
-      </c>
-      <c r="I43" s="9">
-        <f>IFERROR(C43/$B$43*100,"")</f>
-        <v/>
-      </c>
-      <c r="J43" s="9">
-        <f>IFERROR(D43/$B$43*100,"")</f>
-        <v/>
-      </c>
-      <c r="K43" s="9">
-        <f>IFERROR(E43/$B$43*100,"")</f>
-        <v/>
-      </c>
-      <c r="L43" s="9">
-        <f>IFERROR(F43/$B$43*100,"")</f>
-        <v/>
       </c>
     </row>
     <row r="44" ht="16" customHeight="1">
       <c r="A44" s="4" t="inlineStr">
         <is>
-          <t>Reserve for sikringstransaktioner</t>
+          <t>Selskabskapital</t>
         </is>
       </c>
       <c r="B44" s="5">
@@ -2563,7 +2563,7 @@
     <row r="45" ht="16" customHeight="1">
       <c r="A45" s="7" t="inlineStr">
         <is>
-          <t>Andre reserver</t>
+          <t>Reserve for nettoopskrivning (indre værdis metode)</t>
         </is>
       </c>
       <c r="B45" s="8">
@@ -2611,7 +2611,7 @@
     <row r="46" ht="16" customHeight="1">
       <c r="A46" s="4" t="inlineStr">
         <is>
-          <t>Overført resultat</t>
+          <t>Reserve for udviklingsomkostninger</t>
         </is>
       </c>
       <c r="B46" s="5">
@@ -2657,97 +2657,97 @@
       </c>
     </row>
     <row r="47" ht="16" customHeight="1">
-      <c r="A47" s="10" t="inlineStr">
-        <is>
-          <t>Egenkapital i alt</t>
-        </is>
-      </c>
-      <c r="B47" s="11">
+      <c r="A47" s="7" t="inlineStr">
+        <is>
+          <t>Reserve for sikringstransaktioner</t>
+        </is>
+      </c>
+      <c r="B47" s="8">
         <f>'balance_raw'!$B$24</f>
         <v/>
       </c>
-      <c r="C47" s="11">
+      <c r="C47" s="8">
         <f>'balance_raw'!$C$24</f>
         <v/>
       </c>
-      <c r="D47" s="11">
+      <c r="D47" s="8">
         <f>'balance_raw'!$D$24</f>
         <v/>
       </c>
-      <c r="E47" s="11">
+      <c r="E47" s="8">
         <f>'balance_raw'!$E$24</f>
         <v/>
       </c>
-      <c r="F47" s="11">
+      <c r="F47" s="8">
         <f>'balance_raw'!$F$24</f>
         <v/>
       </c>
       <c r="G47" t="inlineStr"/>
-      <c r="H47" s="12">
+      <c r="H47" s="9">
         <f>IFERROR(B47/$B$47*100,"")</f>
         <v/>
       </c>
-      <c r="I47" s="12">
+      <c r="I47" s="9">
         <f>IFERROR(C47/$B$47*100,"")</f>
         <v/>
       </c>
-      <c r="J47" s="12">
+      <c r="J47" s="9">
         <f>IFERROR(D47/$B$47*100,"")</f>
         <v/>
       </c>
-      <c r="K47" s="12">
+      <c r="K47" s="9">
         <f>IFERROR(E47/$B$47*100,"")</f>
         <v/>
       </c>
-      <c r="L47" s="12">
+      <c r="L47" s="9">
         <f>IFERROR(F47/$B$47*100,"")</f>
         <v/>
       </c>
     </row>
     <row r="48" ht="16" customHeight="1">
-      <c r="A48" s="10" t="inlineStr">
-        <is>
-          <t>Hensatte forpligtelser</t>
-        </is>
-      </c>
-      <c r="B48" s="11">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>Andre reserver</t>
+        </is>
+      </c>
+      <c r="B48" s="5">
         <f>'balance_raw'!$B$25</f>
         <v/>
       </c>
-      <c r="C48" s="11">
+      <c r="C48" s="5">
         <f>'balance_raw'!$C$25</f>
         <v/>
       </c>
-      <c r="D48" s="11">
+      <c r="D48" s="5">
         <f>'balance_raw'!$D$25</f>
         <v/>
       </c>
-      <c r="E48" s="11">
+      <c r="E48" s="5">
         <f>'balance_raw'!$E$25</f>
         <v/>
       </c>
-      <c r="F48" s="11">
+      <c r="F48" s="5">
         <f>'balance_raw'!$F$25</f>
         <v/>
       </c>
       <c r="G48" t="inlineStr"/>
-      <c r="H48" s="12">
+      <c r="H48" s="6">
         <f>IFERROR(B48/$B$48*100,"")</f>
         <v/>
       </c>
-      <c r="I48" s="12">
+      <c r="I48" s="6">
         <f>IFERROR(C48/$B$48*100,"")</f>
         <v/>
       </c>
-      <c r="J48" s="12">
+      <c r="J48" s="6">
         <f>IFERROR(D48/$B$48*100,"")</f>
         <v/>
       </c>
-      <c r="K48" s="12">
+      <c r="K48" s="6">
         <f>IFERROR(E48/$B$48*100,"")</f>
         <v/>
       </c>
-      <c r="L48" s="12">
+      <c r="L48" s="6">
         <f>IFERROR(F48/$B$48*100,"")</f>
         <v/>
       </c>
@@ -2755,7 +2755,7 @@
     <row r="49" ht="16" customHeight="1">
       <c r="A49" s="7" t="inlineStr">
         <is>
-          <t>Ansvarlig lånekapital (langfristet)</t>
+          <t>Overført resultat</t>
         </is>
       </c>
       <c r="B49" s="8">
@@ -2801,97 +2801,97 @@
       </c>
     </row>
     <row r="50" ht="16" customHeight="1">
-      <c r="A50" s="4" t="inlineStr">
-        <is>
-          <t>Langfristede lån</t>
-        </is>
-      </c>
-      <c r="B50" s="5">
+      <c r="A50" s="10" t="inlineStr">
+        <is>
+          <t>Egenkapital i alt</t>
+        </is>
+      </c>
+      <c r="B50" s="11">
         <f>'balance_raw'!$B$27</f>
         <v/>
       </c>
-      <c r="C50" s="5">
+      <c r="C50" s="11">
         <f>'balance_raw'!$C$27</f>
         <v/>
       </c>
-      <c r="D50" s="5">
+      <c r="D50" s="11">
         <f>'balance_raw'!$D$27</f>
         <v/>
       </c>
-      <c r="E50" s="5">
+      <c r="E50" s="11">
         <f>'balance_raw'!$E$27</f>
         <v/>
       </c>
-      <c r="F50" s="5">
+      <c r="F50" s="11">
         <f>'balance_raw'!$F$27</f>
         <v/>
       </c>
       <c r="G50" t="inlineStr"/>
-      <c r="H50" s="6">
+      <c r="H50" s="12">
         <f>IFERROR(B50/$B$50*100,"")</f>
         <v/>
       </c>
-      <c r="I50" s="6">
+      <c r="I50" s="12">
         <f>IFERROR(C50/$B$50*100,"")</f>
         <v/>
       </c>
-      <c r="J50" s="6">
+      <c r="J50" s="12">
         <f>IFERROR(D50/$B$50*100,"")</f>
         <v/>
       </c>
-      <c r="K50" s="6">
+      <c r="K50" s="12">
         <f>IFERROR(E50/$B$50*100,"")</f>
         <v/>
       </c>
-      <c r="L50" s="6">
+      <c r="L50" s="12">
         <f>IFERROR(F50/$B$50*100,"")</f>
         <v/>
       </c>
     </row>
     <row r="51" ht="16" customHeight="1">
-      <c r="A51" s="7" t="inlineStr">
-        <is>
-          <t>Leasingforpligtelser (langfristet)</t>
-        </is>
-      </c>
-      <c r="B51" s="8">
+      <c r="A51" s="10" t="inlineStr">
+        <is>
+          <t>Hensatte forpligtelser</t>
+        </is>
+      </c>
+      <c r="B51" s="11">
         <f>'balance_raw'!$B$28</f>
         <v/>
       </c>
-      <c r="C51" s="8">
+      <c r="C51" s="11">
         <f>'balance_raw'!$C$28</f>
         <v/>
       </c>
-      <c r="D51" s="8">
+      <c r="D51" s="11">
         <f>'balance_raw'!$D$28</f>
         <v/>
       </c>
-      <c r="E51" s="8">
+      <c r="E51" s="11">
         <f>'balance_raw'!$E$28</f>
         <v/>
       </c>
-      <c r="F51" s="8">
+      <c r="F51" s="11">
         <f>'balance_raw'!$F$28</f>
         <v/>
       </c>
       <c r="G51" t="inlineStr"/>
-      <c r="H51" s="9">
+      <c r="H51" s="12">
         <f>IFERROR(B51/$B$51*100,"")</f>
         <v/>
       </c>
-      <c r="I51" s="9">
+      <c r="I51" s="12">
         <f>IFERROR(C51/$B$51*100,"")</f>
         <v/>
       </c>
-      <c r="J51" s="9">
+      <c r="J51" s="12">
         <f>IFERROR(D51/$B$51*100,"")</f>
         <v/>
       </c>
-      <c r="K51" s="9">
+      <c r="K51" s="12">
         <f>IFERROR(E51/$B$51*100,"")</f>
         <v/>
       </c>
-      <c r="L51" s="9">
+      <c r="L51" s="12">
         <f>IFERROR(F51/$B$51*100,"")</f>
         <v/>
       </c>
@@ -2899,7 +2899,7 @@
     <row r="52" ht="16" customHeight="1">
       <c r="A52" s="4" t="inlineStr">
         <is>
-          <t>Anden gæld (langfristet)</t>
+          <t>Ansvarlig lånekapital (langfristet)</t>
         </is>
       </c>
       <c r="B52" s="5">
@@ -2945,49 +2945,49 @@
       </c>
     </row>
     <row r="53" ht="16" customHeight="1">
-      <c r="A53" s="10" t="inlineStr">
-        <is>
-          <t>Langfristede gældsforpligtelser</t>
-        </is>
-      </c>
-      <c r="B53" s="11">
+      <c r="A53" s="7" t="inlineStr">
+        <is>
+          <t>Langfristede lån</t>
+        </is>
+      </c>
+      <c r="B53" s="8">
         <f>'balance_raw'!$B$30</f>
         <v/>
       </c>
-      <c r="C53" s="11">
+      <c r="C53" s="8">
         <f>'balance_raw'!$C$30</f>
         <v/>
       </c>
-      <c r="D53" s="11">
+      <c r="D53" s="8">
         <f>'balance_raw'!$D$30</f>
         <v/>
       </c>
-      <c r="E53" s="11">
+      <c r="E53" s="8">
         <f>'balance_raw'!$E$30</f>
         <v/>
       </c>
-      <c r="F53" s="11">
+      <c r="F53" s="8">
         <f>'balance_raw'!$F$30</f>
         <v/>
       </c>
       <c r="G53" t="inlineStr"/>
-      <c r="H53" s="12">
+      <c r="H53" s="9">
         <f>IFERROR(B53/$B$53*100,"")</f>
         <v/>
       </c>
-      <c r="I53" s="12">
+      <c r="I53" s="9">
         <f>IFERROR(C53/$B$53*100,"")</f>
         <v/>
       </c>
-      <c r="J53" s="12">
+      <c r="J53" s="9">
         <f>IFERROR(D53/$B$53*100,"")</f>
         <v/>
       </c>
-      <c r="K53" s="12">
+      <c r="K53" s="9">
         <f>IFERROR(E53/$B$53*100,"")</f>
         <v/>
       </c>
-      <c r="L53" s="12">
+      <c r="L53" s="9">
         <f>IFERROR(F53/$B$53*100,"")</f>
         <v/>
       </c>
@@ -2995,7 +2995,7 @@
     <row r="54" ht="16" customHeight="1">
       <c r="A54" s="4" t="inlineStr">
         <is>
-          <t>Ansvarlig lånekapital (kortfristet)</t>
+          <t>Leasingforpligtelser (langfristet)</t>
         </is>
       </c>
       <c r="B54" s="5">
@@ -3043,7 +3043,7 @@
     <row r="55" ht="16" customHeight="1">
       <c r="A55" s="7" t="inlineStr">
         <is>
-          <t>Kortfristet del af langfristede gældsforpligtelser</t>
+          <t>Anden gæld (langfristet)</t>
         </is>
       </c>
       <c r="B55" s="8">
@@ -3089,49 +3089,49 @@
       </c>
     </row>
     <row r="56" ht="16" customHeight="1">
-      <c r="A56" s="4" t="inlineStr">
-        <is>
-          <t>Kreditinstitutter</t>
-        </is>
-      </c>
-      <c r="B56" s="5">
+      <c r="A56" s="10" t="inlineStr">
+        <is>
+          <t>Langfristede gældsforpligtelser</t>
+        </is>
+      </c>
+      <c r="B56" s="11">
         <f>'balance_raw'!$B$33</f>
         <v/>
       </c>
-      <c r="C56" s="5">
+      <c r="C56" s="11">
         <f>'balance_raw'!$C$33</f>
         <v/>
       </c>
-      <c r="D56" s="5">
+      <c r="D56" s="11">
         <f>'balance_raw'!$D$33</f>
         <v/>
       </c>
-      <c r="E56" s="5">
+      <c r="E56" s="11">
         <f>'balance_raw'!$E$33</f>
         <v/>
       </c>
-      <c r="F56" s="5">
+      <c r="F56" s="11">
         <f>'balance_raw'!$F$33</f>
         <v/>
       </c>
       <c r="G56" t="inlineStr"/>
-      <c r="H56" s="6">
+      <c r="H56" s="12">
         <f>IFERROR(B56/$B$56*100,"")</f>
         <v/>
       </c>
-      <c r="I56" s="6">
+      <c r="I56" s="12">
         <f>IFERROR(C56/$B$56*100,"")</f>
         <v/>
       </c>
-      <c r="J56" s="6">
+      <c r="J56" s="12">
         <f>IFERROR(D56/$B$56*100,"")</f>
         <v/>
       </c>
-      <c r="K56" s="6">
+      <c r="K56" s="12">
         <f>IFERROR(E56/$B$56*100,"")</f>
         <v/>
       </c>
-      <c r="L56" s="6">
+      <c r="L56" s="12">
         <f>IFERROR(F56/$B$56*100,"")</f>
         <v/>
       </c>
@@ -3139,7 +3139,7 @@
     <row r="57" ht="16" customHeight="1">
       <c r="A57" s="7" t="inlineStr">
         <is>
-          <t>Leasingforpligtelser (kortfristet)</t>
+          <t>Ansvarlig lånekapital (kortfristet)</t>
         </is>
       </c>
       <c r="B57" s="8">
@@ -3187,7 +3187,7 @@
     <row r="58" ht="16" customHeight="1">
       <c r="A58" s="4" t="inlineStr">
         <is>
-          <t>Leverandører af varer og tjenesteydelser</t>
+          <t>Kortfristet del af langfristede gældsforpligtelser</t>
         </is>
       </c>
       <c r="B58" s="5">
@@ -3235,7 +3235,7 @@
     <row r="59" ht="16" customHeight="1">
       <c r="A59" s="7" t="inlineStr">
         <is>
-          <t>Gæld til tilknyttede virksomheder</t>
+          <t>Kreditinstitutter</t>
         </is>
       </c>
       <c r="B59" s="8">
@@ -3283,7 +3283,7 @@
     <row r="60" ht="16" customHeight="1">
       <c r="A60" s="4" t="inlineStr">
         <is>
-          <t>Gæld til selskabsdeltagere og ledelse</t>
+          <t>Leasingforpligtelser (kortfristet)</t>
         </is>
       </c>
       <c r="B60" s="5">
@@ -3331,7 +3331,7 @@
     <row r="61" ht="16" customHeight="1">
       <c r="A61" s="7" t="inlineStr">
         <is>
-          <t>Selskabsskat</t>
+          <t>Leverandører af varer og tjenesteydelser</t>
         </is>
       </c>
       <c r="B61" s="8">
@@ -3379,7 +3379,7 @@
     <row r="62" ht="16" customHeight="1">
       <c r="A62" s="4" t="inlineStr">
         <is>
-          <t>Gæld til tilknyttede virksomheder vedr. selskabsskat</t>
+          <t>Gæld til tilknyttede virksomheder</t>
         </is>
       </c>
       <c r="B62" s="5">
@@ -3427,7 +3427,7 @@
     <row r="63" ht="16" customHeight="1">
       <c r="A63" s="7" t="inlineStr">
         <is>
-          <t>Anden gæld (kortfristet)</t>
+          <t>Gæld til selskabsdeltagere og ledelse</t>
         </is>
       </c>
       <c r="B63" s="8">
@@ -3475,7 +3475,7 @@
     <row r="64" ht="16" customHeight="1">
       <c r="A64" s="4" t="inlineStr">
         <is>
-          <t>Periodeafgrænsningsposter (passiver)</t>
+          <t>Selskabsskat</t>
         </is>
       </c>
       <c r="B64" s="5">
@@ -3521,583 +3521,727 @@
       </c>
     </row>
     <row r="65" ht="16" customHeight="1">
-      <c r="A65" s="10" t="inlineStr">
+      <c r="A65" s="7" t="inlineStr">
+        <is>
+          <t>Gæld til tilknyttede virksomheder vedr. selskabsskat</t>
+        </is>
+      </c>
+      <c r="B65" s="8">
+        <f>'balance_raw'!$B$42</f>
+        <v/>
+      </c>
+      <c r="C65" s="8">
+        <f>'balance_raw'!$C$42</f>
+        <v/>
+      </c>
+      <c r="D65" s="8">
+        <f>'balance_raw'!$D$42</f>
+        <v/>
+      </c>
+      <c r="E65" s="8">
+        <f>'balance_raw'!$E$42</f>
+        <v/>
+      </c>
+      <c r="F65" s="8">
+        <f>'balance_raw'!$F$42</f>
+        <v/>
+      </c>
+      <c r="G65" t="inlineStr"/>
+      <c r="H65" s="9">
+        <f>IFERROR(B65/$B$65*100,"")</f>
+        <v/>
+      </c>
+      <c r="I65" s="9">
+        <f>IFERROR(C65/$B$65*100,"")</f>
+        <v/>
+      </c>
+      <c r="J65" s="9">
+        <f>IFERROR(D65/$B$65*100,"")</f>
+        <v/>
+      </c>
+      <c r="K65" s="9">
+        <f>IFERROR(E65/$B$65*100,"")</f>
+        <v/>
+      </c>
+      <c r="L65" s="9">
+        <f>IFERROR(F65/$B$65*100,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="66" ht="16" customHeight="1">
+      <c r="A66" s="4" t="inlineStr">
+        <is>
+          <t>Anden gæld (kortfristet)</t>
+        </is>
+      </c>
+      <c r="B66" s="5">
+        <f>'balance_raw'!$B$43</f>
+        <v/>
+      </c>
+      <c r="C66" s="5">
+        <f>'balance_raw'!$C$43</f>
+        <v/>
+      </c>
+      <c r="D66" s="5">
+        <f>'balance_raw'!$D$43</f>
+        <v/>
+      </c>
+      <c r="E66" s="5">
+        <f>'balance_raw'!$E$43</f>
+        <v/>
+      </c>
+      <c r="F66" s="5">
+        <f>'balance_raw'!$F$43</f>
+        <v/>
+      </c>
+      <c r="G66" t="inlineStr"/>
+      <c r="H66" s="6">
+        <f>IFERROR(B66/$B$66*100,"")</f>
+        <v/>
+      </c>
+      <c r="I66" s="6">
+        <f>IFERROR(C66/$B$66*100,"")</f>
+        <v/>
+      </c>
+      <c r="J66" s="6">
+        <f>IFERROR(D66/$B$66*100,"")</f>
+        <v/>
+      </c>
+      <c r="K66" s="6">
+        <f>IFERROR(E66/$B$66*100,"")</f>
+        <v/>
+      </c>
+      <c r="L66" s="6">
+        <f>IFERROR(F66/$B$66*100,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="67" ht="16" customHeight="1">
+      <c r="A67" s="7" t="inlineStr">
+        <is>
+          <t>Periodeafgrænsningsposter (passiver)</t>
+        </is>
+      </c>
+      <c r="B67" s="8">
+        <f>'balance_raw'!$B$44</f>
+        <v/>
+      </c>
+      <c r="C67" s="8">
+        <f>'balance_raw'!$C$44</f>
+        <v/>
+      </c>
+      <c r="D67" s="8">
+        <f>'balance_raw'!$D$44</f>
+        <v/>
+      </c>
+      <c r="E67" s="8">
+        <f>'balance_raw'!$E$44</f>
+        <v/>
+      </c>
+      <c r="F67" s="8">
+        <f>'balance_raw'!$F$44</f>
+        <v/>
+      </c>
+      <c r="G67" t="inlineStr"/>
+      <c r="H67" s="9">
+        <f>IFERROR(B67/$B$67*100,"")</f>
+        <v/>
+      </c>
+      <c r="I67" s="9">
+        <f>IFERROR(C67/$B$67*100,"")</f>
+        <v/>
+      </c>
+      <c r="J67" s="9">
+        <f>IFERROR(D67/$B$67*100,"")</f>
+        <v/>
+      </c>
+      <c r="K67" s="9">
+        <f>IFERROR(E67/$B$67*100,"")</f>
+        <v/>
+      </c>
+      <c r="L67" s="9">
+        <f>IFERROR(F67/$B$67*100,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="68" ht="16" customHeight="1">
+      <c r="A68" s="10" t="inlineStr">
         <is>
           <t>Kortfristede gældsforpligtelser</t>
         </is>
       </c>
-      <c r="B65" s="11">
-        <f>'balance_raw'!$B$42</f>
-        <v/>
-      </c>
-      <c r="C65" s="11">
-        <f>'balance_raw'!$C$42</f>
-        <v/>
-      </c>
-      <c r="D65" s="11">
-        <f>'balance_raw'!$D$42</f>
-        <v/>
-      </c>
-      <c r="E65" s="11">
-        <f>'balance_raw'!$E$42</f>
-        <v/>
-      </c>
-      <c r="F65" s="11">
-        <f>'balance_raw'!$F$42</f>
-        <v/>
-      </c>
-      <c r="G65" t="inlineStr"/>
-      <c r="H65" s="12">
-        <f>IFERROR(B65/$B$65*100,"")</f>
-        <v/>
-      </c>
-      <c r="I65" s="12">
-        <f>IFERROR(C65/$B$65*100,"")</f>
-        <v/>
-      </c>
-      <c r="J65" s="12">
-        <f>IFERROR(D65/$B$65*100,"")</f>
-        <v/>
-      </c>
-      <c r="K65" s="12">
-        <f>IFERROR(E65/$B$65*100,"")</f>
-        <v/>
-      </c>
-      <c r="L65" s="12">
-        <f>IFERROR(F65/$B$65*100,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="66" ht="16" customHeight="1">
-      <c r="A66" s="10" t="inlineStr">
+      <c r="B68" s="11">
+        <f>'balance_raw'!$B$45</f>
+        <v/>
+      </c>
+      <c r="C68" s="11">
+        <f>'balance_raw'!$C$45</f>
+        <v/>
+      </c>
+      <c r="D68" s="11">
+        <f>'balance_raw'!$D$45</f>
+        <v/>
+      </c>
+      <c r="E68" s="11">
+        <f>'balance_raw'!$E$45</f>
+        <v/>
+      </c>
+      <c r="F68" s="11">
+        <f>'balance_raw'!$F$45</f>
+        <v/>
+      </c>
+      <c r="G68" t="inlineStr"/>
+      <c r="H68" s="12">
+        <f>IFERROR(B68/$B$68*100,"")</f>
+        <v/>
+      </c>
+      <c r="I68" s="12">
+        <f>IFERROR(C68/$B$68*100,"")</f>
+        <v/>
+      </c>
+      <c r="J68" s="12">
+        <f>IFERROR(D68/$B$68*100,"")</f>
+        <v/>
+      </c>
+      <c r="K68" s="12">
+        <f>IFERROR(E68/$B$68*100,"")</f>
+        <v/>
+      </c>
+      <c r="L68" s="12">
+        <f>IFERROR(F68/$B$68*100,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="69" ht="16" customHeight="1">
+      <c r="A69" s="10" t="inlineStr">
         <is>
           <t>Gældsforpligtelser</t>
         </is>
       </c>
-      <c r="B66" s="11">
-        <f>'balance_raw'!$B$43</f>
-        <v/>
-      </c>
-      <c r="C66" s="11">
-        <f>'balance_raw'!$C$43</f>
-        <v/>
-      </c>
-      <c r="D66" s="11">
-        <f>'balance_raw'!$D$43</f>
-        <v/>
-      </c>
-      <c r="E66" s="11">
-        <f>'balance_raw'!$E$43</f>
-        <v/>
-      </c>
-      <c r="F66" s="11">
-        <f>'balance_raw'!$F$43</f>
-        <v/>
-      </c>
-      <c r="G66" t="inlineStr"/>
-      <c r="H66" s="12">
-        <f>IFERROR(B66/$B$66*100,"")</f>
-        <v/>
-      </c>
-      <c r="I66" s="12">
-        <f>IFERROR(C66/$B$66*100,"")</f>
-        <v/>
-      </c>
-      <c r="J66" s="12">
-        <f>IFERROR(D66/$B$66*100,"")</f>
-        <v/>
-      </c>
-      <c r="K66" s="12">
-        <f>IFERROR(E66/$B$66*100,"")</f>
-        <v/>
-      </c>
-      <c r="L66" s="12">
-        <f>IFERROR(F66/$B$66*100,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="67" ht="16" customHeight="1">
-      <c r="A67" s="10" t="inlineStr">
+      <c r="B69" s="11">
+        <f>'balance_raw'!$B$46</f>
+        <v/>
+      </c>
+      <c r="C69" s="11">
+        <f>'balance_raw'!$C$46</f>
+        <v/>
+      </c>
+      <c r="D69" s="11">
+        <f>'balance_raw'!$D$46</f>
+        <v/>
+      </c>
+      <c r="E69" s="11">
+        <f>'balance_raw'!$E$46</f>
+        <v/>
+      </c>
+      <c r="F69" s="11">
+        <f>'balance_raw'!$F$46</f>
+        <v/>
+      </c>
+      <c r="G69" t="inlineStr"/>
+      <c r="H69" s="12">
+        <f>IFERROR(B69/$B$69*100,"")</f>
+        <v/>
+      </c>
+      <c r="I69" s="12">
+        <f>IFERROR(C69/$B$69*100,"")</f>
+        <v/>
+      </c>
+      <c r="J69" s="12">
+        <f>IFERROR(D69/$B$69*100,"")</f>
+        <v/>
+      </c>
+      <c r="K69" s="12">
+        <f>IFERROR(E69/$B$69*100,"")</f>
+        <v/>
+      </c>
+      <c r="L69" s="12">
+        <f>IFERROR(F69/$B$69*100,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="70" ht="16" customHeight="1">
+      <c r="A70" s="10" t="inlineStr">
         <is>
           <t>Passiver</t>
         </is>
       </c>
-      <c r="B67" s="11">
-        <f>'balance_raw'!$B$44</f>
-        <v/>
-      </c>
-      <c r="C67" s="11">
-        <f>'balance_raw'!$C$44</f>
-        <v/>
-      </c>
-      <c r="D67" s="11">
-        <f>'balance_raw'!$D$44</f>
-        <v/>
-      </c>
-      <c r="E67" s="11">
-        <f>'balance_raw'!$E$44</f>
-        <v/>
-      </c>
-      <c r="F67" s="11">
-        <f>'balance_raw'!$F$44</f>
-        <v/>
-      </c>
-      <c r="G67" t="inlineStr"/>
-      <c r="H67" s="12">
-        <f>IFERROR(B67/$B$67*100,"")</f>
-        <v/>
-      </c>
-      <c r="I67" s="12">
-        <f>IFERROR(C67/$B$67*100,"")</f>
-        <v/>
-      </c>
-      <c r="J67" s="12">
-        <f>IFERROR(D67/$B$67*100,"")</f>
-        <v/>
-      </c>
-      <c r="K67" s="12">
-        <f>IFERROR(E67/$B$67*100,"")</f>
-        <v/>
-      </c>
-      <c r="L67" s="12">
-        <f>IFERROR(F67/$B$67*100,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="69" ht="22" customHeight="1">
-      <c r="A69" s="3" t="inlineStr">
+      <c r="B70" s="11">
+        <f>'balance_raw'!$B$47</f>
+        <v/>
+      </c>
+      <c r="C70" s="11">
+        <f>'balance_raw'!$C$47</f>
+        <v/>
+      </c>
+      <c r="D70" s="11">
+        <f>'balance_raw'!$D$47</f>
+        <v/>
+      </c>
+      <c r="E70" s="11">
+        <f>'balance_raw'!$E$47</f>
+        <v/>
+      </c>
+      <c r="F70" s="11">
+        <f>'balance_raw'!$F$47</f>
+        <v/>
+      </c>
+      <c r="G70" t="inlineStr"/>
+      <c r="H70" s="12">
+        <f>IFERROR(B70/$B$70*100,"")</f>
+        <v/>
+      </c>
+      <c r="I70" s="12">
+        <f>IFERROR(C70/$B$70*100,"")</f>
+        <v/>
+      </c>
+      <c r="J70" s="12">
+        <f>IFERROR(D70/$B$70*100,"")</f>
+        <v/>
+      </c>
+      <c r="K70" s="12">
+        <f>IFERROR(E70/$B$70*100,"")</f>
+        <v/>
+      </c>
+      <c r="L70" s="12">
+        <f>IFERROR(F70/$B$70*100,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="72" ht="22" customHeight="1">
+      <c r="A72" s="3" t="inlineStr">
         <is>
           <t>NØGLEOPLYSNINGER</t>
         </is>
       </c>
-      <c r="B69" s="3" t="n">
+      <c r="B72" s="3" t="n">
         <v>2020</v>
       </c>
-      <c r="C69" s="3" t="n">
+      <c r="C72" s="3" t="n">
         <v>2021</v>
       </c>
-      <c r="D69" s="3" t="n">
+      <c r="D72" s="3" t="n">
         <v>2022</v>
       </c>
-      <c r="E69" s="3" t="n">
+      <c r="E72" s="3" t="n">
         <v>2023</v>
       </c>
-      <c r="F69" s="3" t="n">
+      <c r="F72" s="3" t="n">
         <v>2024</v>
       </c>
     </row>
-    <row r="70" ht="16" customHeight="1">
-      <c r="A70" s="4" t="inlineStr">
+    <row r="73" ht="16" customHeight="1">
+      <c r="A73" s="7" t="inlineStr">
         <is>
           <t>Gns. antal medarbejdere</t>
         </is>
       </c>
-      <c r="B70" s="5">
+      <c r="B73" s="8">
         <f>'res_raw'!$B$19</f>
         <v/>
       </c>
-      <c r="C70" s="5">
+      <c r="C73" s="8">
         <f>'res_raw'!$C$19</f>
         <v/>
       </c>
-      <c r="D70" s="5">
+      <c r="D73" s="8">
         <f>'res_raw'!$D$19</f>
         <v/>
       </c>
-      <c r="E70" s="5">
+      <c r="E73" s="8">
         <f>'res_raw'!$E$19</f>
         <v/>
       </c>
-      <c r="F70" s="5">
+      <c r="F73" s="8">
         <f>'res_raw'!$F$19</f>
         <v/>
       </c>
-      <c r="G70" t="inlineStr"/>
-      <c r="H70" s="6">
-        <f>IFERROR(B70/$B$70*100,"")</f>
-        <v/>
-      </c>
-      <c r="I70" s="6">
-        <f>IFERROR(C70/$B$70*100,"")</f>
-        <v/>
-      </c>
-      <c r="J70" s="6">
-        <f>IFERROR(D70/$B$70*100,"")</f>
-        <v/>
-      </c>
-      <c r="K70" s="6">
-        <f>IFERROR(E70/$B$70*100,"")</f>
-        <v/>
-      </c>
-      <c r="L70" s="6">
-        <f>IFERROR(F70/$B$70*100,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="71" ht="16" customHeight="1">
-      <c r="A71" s="7" t="inlineStr">
-        <is>
-          <t>Investering i materielle anlægsaktiver</t>
-        </is>
-      </c>
-      <c r="B71" s="8">
-        <f>'res_raw'!$B$20</f>
-        <v/>
-      </c>
-      <c r="C71" s="8">
-        <f>'res_raw'!$C$20</f>
-        <v/>
-      </c>
-      <c r="D71" s="8">
-        <f>'res_raw'!$D$20</f>
-        <v/>
-      </c>
-      <c r="E71" s="8">
-        <f>'res_raw'!$E$20</f>
-        <v/>
-      </c>
-      <c r="F71" s="8">
-        <f>'res_raw'!$F$20</f>
-        <v/>
-      </c>
-      <c r="G71" t="inlineStr"/>
-      <c r="H71" s="9">
-        <f>IFERROR(B71/$B$71*100,"")</f>
-        <v/>
-      </c>
-      <c r="I71" s="9">
-        <f>IFERROR(C71/$B$71*100,"")</f>
-        <v/>
-      </c>
-      <c r="J71" s="9">
-        <f>IFERROR(D71/$B$71*100,"")</f>
-        <v/>
-      </c>
-      <c r="K71" s="9">
-        <f>IFERROR(E71/$B$71*100,"")</f>
-        <v/>
-      </c>
-      <c r="L71" s="9">
-        <f>IFERROR(F71/$B$71*100,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="73" ht="22" customHeight="1">
-      <c r="A73" s="3" t="inlineStr">
-        <is>
-          <t>NØGLETAL</t>
-        </is>
-      </c>
-      <c r="B73" s="3" t="n">
-        <v>2020</v>
-      </c>
-      <c r="C73" s="3" t="n">
-        <v>2021</v>
-      </c>
-      <c r="D73" s="3" t="n">
-        <v>2022</v>
-      </c>
-      <c r="E73" s="3" t="n">
-        <v>2023</v>
-      </c>
-      <c r="F73" s="3" t="n">
-        <v>2024</v>
+      <c r="G73" t="inlineStr"/>
+      <c r="H73" s="9">
+        <f>IFERROR(B73/$B$73*100,"")</f>
+        <v/>
+      </c>
+      <c r="I73" s="9">
+        <f>IFERROR(C73/$B$73*100,"")</f>
+        <v/>
+      </c>
+      <c r="J73" s="9">
+        <f>IFERROR(D73/$B$73*100,"")</f>
+        <v/>
+      </c>
+      <c r="K73" s="9">
+        <f>IFERROR(E73/$B$73*100,"")</f>
+        <v/>
+      </c>
+      <c r="L73" s="9">
+        <f>IFERROR(F73/$B$73*100,"")</f>
+        <v/>
       </c>
     </row>
     <row r="74" ht="16" customHeight="1">
       <c r="A74" s="4" t="inlineStr">
         <is>
-          <t>Afkastningsgrad, %</t>
-        </is>
-      </c>
-      <c r="B74" s="13">
-        <f>IFERROR(($B$13+$B$15+$B$14)/$B$38*100,"")</f>
-        <v/>
-      </c>
-      <c r="C74" s="13">
-        <f>IFERROR(($C$13+$C$15+$C$14)/$C$38*100,"")</f>
-        <v/>
-      </c>
-      <c r="D74" s="13">
-        <f>IFERROR(($D$13+$D$15+$D$14)/$D$38*100,"")</f>
-        <v/>
-      </c>
-      <c r="E74" s="13">
-        <f>IFERROR(($E$13+$E$15+$E$14)/$E$38*100,"")</f>
-        <v/>
-      </c>
-      <c r="F74" s="13">
-        <f>IFERROR(($F$13+$F$15+$F$14)/$F$38*100,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="75" ht="16" customHeight="1">
-      <c r="A75" s="7" t="inlineStr">
-        <is>
-          <t>Overskudsgrad, %</t>
-        </is>
-      </c>
-      <c r="B75" s="14">
-        <f>IFERROR(($B$13+$B$15+$B$14)/$B$4*100,"")</f>
-        <v/>
-      </c>
-      <c r="C75" s="14">
-        <f>IFERROR(($C$13+$C$15+$C$14)/$C$4*100,"")</f>
-        <v/>
-      </c>
-      <c r="D75" s="14">
-        <f>IFERROR(($D$13+$D$15+$D$14)/$D$4*100,"")</f>
-        <v/>
-      </c>
-      <c r="E75" s="14">
-        <f>IFERROR(($E$13+$E$15+$E$14)/$E$4*100,"")</f>
-        <v/>
-      </c>
-      <c r="F75" s="14">
-        <f>IFERROR(($F$13+$F$15+$F$14)/$F$4*100,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="76" ht="16" customHeight="1">
-      <c r="A76" s="4" t="inlineStr">
-        <is>
-          <t>Aktivernes omsætningshastighed, gange</t>
-        </is>
-      </c>
-      <c r="B76" s="13">
-        <f>IFERROR($B$4/$B$38,"")</f>
-        <v/>
-      </c>
-      <c r="C76" s="13">
-        <f>IFERROR($C$4/$C$38,"")</f>
-        <v/>
-      </c>
-      <c r="D76" s="13">
-        <f>IFERROR($D$4/$D$38,"")</f>
-        <v/>
-      </c>
-      <c r="E76" s="13">
-        <f>IFERROR($E$4/$E$38,"")</f>
-        <v/>
-      </c>
-      <c r="F76" s="13">
-        <f>IFERROR($F$4/$F$38,"")</f>
-        <v/>
+          <t>Investering i materielle anlægsaktiver</t>
+        </is>
+      </c>
+      <c r="B74" s="5">
+        <f>'res_raw'!$B$20</f>
+        <v/>
+      </c>
+      <c r="C74" s="5">
+        <f>'res_raw'!$C$20</f>
+        <v/>
+      </c>
+      <c r="D74" s="5">
+        <f>'res_raw'!$D$20</f>
+        <v/>
+      </c>
+      <c r="E74" s="5">
+        <f>'res_raw'!$E$20</f>
+        <v/>
+      </c>
+      <c r="F74" s="5">
+        <f>'res_raw'!$F$20</f>
+        <v/>
+      </c>
+      <c r="G74" t="inlineStr"/>
+      <c r="H74" s="6">
+        <f>IFERROR(B74/$B$74*100,"")</f>
+        <v/>
+      </c>
+      <c r="I74" s="6">
+        <f>IFERROR(C74/$B$74*100,"")</f>
+        <v/>
+      </c>
+      <c r="J74" s="6">
+        <f>IFERROR(D74/$B$74*100,"")</f>
+        <v/>
+      </c>
+      <c r="K74" s="6">
+        <f>IFERROR(E74/$B$74*100,"")</f>
+        <v/>
+      </c>
+      <c r="L74" s="6">
+        <f>IFERROR(F74/$B$74*100,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="76" ht="22" customHeight="1">
+      <c r="A76" s="3" t="inlineStr">
+        <is>
+          <t>NØGLETAL</t>
+        </is>
+      </c>
+      <c r="B76" s="3" t="n">
+        <v>2020</v>
+      </c>
+      <c r="C76" s="3" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D76" s="3" t="n">
+        <v>2022</v>
+      </c>
+      <c r="E76" s="3" t="n">
+        <v>2023</v>
+      </c>
+      <c r="F76" s="3" t="n">
+        <v>2024</v>
       </c>
     </row>
     <row r="77" ht="16" customHeight="1">
       <c r="A77" s="7" t="inlineStr">
         <is>
-          <t>Egenkapitalens forrentning, %</t>
-        </is>
-      </c>
-      <c r="B77" s="14">
-        <f>IFERROR($B$18/$B$47*100,"")</f>
-        <v/>
-      </c>
-      <c r="C77" s="14">
-        <f>IFERROR($C$18/$C$47*100,"")</f>
-        <v/>
-      </c>
-      <c r="D77" s="14">
-        <f>IFERROR($D$18/$D$47*100,"")</f>
-        <v/>
-      </c>
-      <c r="E77" s="14">
-        <f>IFERROR($E$18/$E$47*100,"")</f>
-        <v/>
-      </c>
-      <c r="F77" s="14">
-        <f>IFERROR($F$18/$F$47*100,"")</f>
+          <t>Afkastningsgrad, %</t>
+        </is>
+      </c>
+      <c r="B77" s="13">
+        <f>IFERROR(($B$13+$B$15+$B$14)/$B$41*100,"")</f>
+        <v/>
+      </c>
+      <c r="C77" s="13">
+        <f>IFERROR(($C$13+$C$15+$C$14)/$C$41*100,"")</f>
+        <v/>
+      </c>
+      <c r="D77" s="13">
+        <f>IFERROR(($D$13+$D$15+$D$14)/$D$41*100,"")</f>
+        <v/>
+      </c>
+      <c r="E77" s="13">
+        <f>IFERROR(($E$13+$E$15+$E$14)/$E$41*100,"")</f>
+        <v/>
+      </c>
+      <c r="F77" s="13">
+        <f>IFERROR(($F$13+$F$15+$F$14)/$F$41*100,"")</f>
         <v/>
       </c>
     </row>
     <row r="78" ht="16" customHeight="1">
       <c r="A78" s="4" t="inlineStr">
         <is>
-          <t>Gældsrente, %</t>
-        </is>
-      </c>
-      <c r="B78" s="13">
-        <f>IFERROR($B$16/($B$67-$B$47)*100,"")</f>
-        <v/>
-      </c>
-      <c r="C78" s="13">
-        <f>IFERROR($C$16/($C$67-$C$47)*100,"")</f>
-        <v/>
-      </c>
-      <c r="D78" s="13">
-        <f>IFERROR($D$16/($D$67-$D$47)*100,"")</f>
-        <v/>
-      </c>
-      <c r="E78" s="13">
-        <f>IFERROR($E$16/($E$67-$E$47)*100,"")</f>
-        <v/>
-      </c>
-      <c r="F78" s="13">
-        <f>IFERROR($F$16/($F$67-$F$47)*100,"")</f>
+          <t>Overskudsgrad, %</t>
+        </is>
+      </c>
+      <c r="B78" s="14">
+        <f>IFERROR(($B$13+$B$15+$B$14)/$B$4*100,"")</f>
+        <v/>
+      </c>
+      <c r="C78" s="14">
+        <f>IFERROR(($C$13+$C$15+$C$14)/$C$4*100,"")</f>
+        <v/>
+      </c>
+      <c r="D78" s="14">
+        <f>IFERROR(($D$13+$D$15+$D$14)/$D$4*100,"")</f>
+        <v/>
+      </c>
+      <c r="E78" s="14">
+        <f>IFERROR(($E$13+$E$15+$E$14)/$E$4*100,"")</f>
+        <v/>
+      </c>
+      <c r="F78" s="14">
+        <f>IFERROR(($F$13+$F$15+$F$14)/$F$4*100,"")</f>
         <v/>
       </c>
     </row>
     <row r="79" ht="16" customHeight="1">
       <c r="A79" s="7" t="inlineStr">
         <is>
-          <t>Soliditetsgrad, %</t>
-        </is>
-      </c>
-      <c r="B79" s="14">
-        <f>IFERROR($B$47/$B$38*100,"")</f>
-        <v/>
-      </c>
-      <c r="C79" s="14">
-        <f>IFERROR($C$47/$C$38*100,"")</f>
-        <v/>
-      </c>
-      <c r="D79" s="14">
-        <f>IFERROR($D$47/$D$38*100,"")</f>
-        <v/>
-      </c>
-      <c r="E79" s="14">
-        <f>IFERROR($E$47/$E$38*100,"")</f>
-        <v/>
-      </c>
-      <c r="F79" s="14">
-        <f>IFERROR($F$47/$F$38*100,"")</f>
+          <t>Aktivernes omsætningshastighed, gange</t>
+        </is>
+      </c>
+      <c r="B79" s="13">
+        <f>IFERROR($B$4/$B$41,"")</f>
+        <v/>
+      </c>
+      <c r="C79" s="13">
+        <f>IFERROR($C$4/$C$41,"")</f>
+        <v/>
+      </c>
+      <c r="D79" s="13">
+        <f>IFERROR($D$4/$D$41,"")</f>
+        <v/>
+      </c>
+      <c r="E79" s="13">
+        <f>IFERROR($E$4/$E$41,"")</f>
+        <v/>
+      </c>
+      <c r="F79" s="13">
+        <f>IFERROR($F$4/$F$41,"")</f>
         <v/>
       </c>
     </row>
     <row r="80" ht="16" customHeight="1">
       <c r="A80" s="4" t="inlineStr">
         <is>
-          <t>Gearing</t>
-        </is>
-      </c>
-      <c r="B80" s="13">
-        <f>IFERROR(($B$67-$B$47)/$B$47,"")</f>
-        <v/>
-      </c>
-      <c r="C80" s="13">
-        <f>IFERROR(($C$67-$C$47)/$C$47,"")</f>
-        <v/>
-      </c>
-      <c r="D80" s="13">
-        <f>IFERROR(($D$67-$D$47)/$D$47,"")</f>
-        <v/>
-      </c>
-      <c r="E80" s="13">
-        <f>IFERROR(($E$67-$E$47)/$E$47,"")</f>
-        <v/>
-      </c>
-      <c r="F80" s="13">
-        <f>IFERROR(($F$67-$F$47)/$F$47,"")</f>
+          <t>Egenkapitalens forrentning, %</t>
+        </is>
+      </c>
+      <c r="B80" s="14">
+        <f>IFERROR($B$18/$B$50*100,"")</f>
+        <v/>
+      </c>
+      <c r="C80" s="14">
+        <f>IFERROR($C$18/$C$50*100,"")</f>
+        <v/>
+      </c>
+      <c r="D80" s="14">
+        <f>IFERROR($D$18/$D$50*100,"")</f>
+        <v/>
+      </c>
+      <c r="E80" s="14">
+        <f>IFERROR($E$18/$E$50*100,"")</f>
+        <v/>
+      </c>
+      <c r="F80" s="14">
+        <f>IFERROR($F$18/$F$50*100,"")</f>
         <v/>
       </c>
     </row>
     <row r="81" ht="16" customHeight="1">
       <c r="A81" s="7" t="inlineStr">
         <is>
-          <t>Likviditetsgrad, %</t>
-        </is>
-      </c>
-      <c r="B81" s="14">
-        <f>IFERROR($B$37/$B$65*100,"")</f>
-        <v/>
-      </c>
-      <c r="C81" s="14">
-        <f>IFERROR($C$37/$C$65*100,"")</f>
-        <v/>
-      </c>
-      <c r="D81" s="14">
-        <f>IFERROR($D$37/$D$65*100,"")</f>
-        <v/>
-      </c>
-      <c r="E81" s="14">
-        <f>IFERROR($E$37/$E$65*100,"")</f>
-        <v/>
-      </c>
-      <c r="F81" s="14">
-        <f>IFERROR($F$37/$F$65*100,"")</f>
+          <t>Gældsrente, %</t>
+        </is>
+      </c>
+      <c r="B81" s="13">
+        <f>IFERROR($B$16/($B$70-$B$50)*100,"")</f>
+        <v/>
+      </c>
+      <c r="C81" s="13">
+        <f>IFERROR($C$16/($C$70-$C$50)*100,"")</f>
+        <v/>
+      </c>
+      <c r="D81" s="13">
+        <f>IFERROR($D$16/($D$70-$D$50)*100,"")</f>
+        <v/>
+      </c>
+      <c r="E81" s="13">
+        <f>IFERROR($E$16/($E$70-$E$50)*100,"")</f>
+        <v/>
+      </c>
+      <c r="F81" s="13">
+        <f>IFERROR($F$16/($F$70-$F$50)*100,"")</f>
         <v/>
       </c>
     </row>
     <row r="82" ht="16" customHeight="1">
       <c r="A82" s="4" t="inlineStr">
         <is>
-          <t>Rentemarginal, %</t>
-        </is>
-      </c>
-      <c r="B82" s="13">
-        <f>IFERROR(B74-B78,"")</f>
-        <v/>
-      </c>
-      <c r="C82" s="13">
-        <f>IFERROR(C74-C78,"")</f>
-        <v/>
-      </c>
-      <c r="D82" s="13">
-        <f>IFERROR(D74-D78,"")</f>
-        <v/>
-      </c>
-      <c r="E82" s="13">
-        <f>IFERROR(E74-E78,"")</f>
-        <v/>
-      </c>
-      <c r="F82" s="13">
-        <f>IFERROR(F74-F78,"")</f>
+          <t>Soliditetsgrad, %</t>
+        </is>
+      </c>
+      <c r="B82" s="14">
+        <f>IFERROR($B$50/$B$41*100,"")</f>
+        <v/>
+      </c>
+      <c r="C82" s="14">
+        <f>IFERROR($C$50/$C$41*100,"")</f>
+        <v/>
+      </c>
+      <c r="D82" s="14">
+        <f>IFERROR($D$50/$D$41*100,"")</f>
+        <v/>
+      </c>
+      <c r="E82" s="14">
+        <f>IFERROR($E$50/$E$41*100,"")</f>
+        <v/>
+      </c>
+      <c r="F82" s="14">
+        <f>IFERROR($F$50/$F$41*100,"")</f>
         <v/>
       </c>
     </row>
     <row r="83" ht="16" customHeight="1">
       <c r="A83" s="7" t="inlineStr">
         <is>
-          <t>Gældsandel, %</t>
-        </is>
-      </c>
-      <c r="B83" s="14">
-        <f>IFERROR(($B$67-$B$47)/$B$38*100,"")</f>
-        <v/>
-      </c>
-      <c r="C83" s="14">
-        <f>IFERROR(($C$67-$C$47)/$C$38*100,"")</f>
-        <v/>
-      </c>
-      <c r="D83" s="14">
-        <f>IFERROR(($D$67-$D$47)/$D$38*100,"")</f>
-        <v/>
-      </c>
-      <c r="E83" s="14">
-        <f>IFERROR(($E$67-$E$47)/$E$38*100,"")</f>
-        <v/>
-      </c>
-      <c r="F83" s="14">
-        <f>IFERROR(($F$67-$F$47)/$F$38*100,"")</f>
+          <t>Gearing</t>
+        </is>
+      </c>
+      <c r="B83" s="13">
+        <f>IFERROR(($B$70-$B$50)/$B$50,"")</f>
+        <v/>
+      </c>
+      <c r="C83" s="13">
+        <f>IFERROR(($C$70-$C$50)/$C$50,"")</f>
+        <v/>
+      </c>
+      <c r="D83" s="13">
+        <f>IFERROR(($D$70-$D$50)/$D$50,"")</f>
+        <v/>
+      </c>
+      <c r="E83" s="13">
+        <f>IFERROR(($E$70-$E$50)/$E$50,"")</f>
+        <v/>
+      </c>
+      <c r="F83" s="13">
+        <f>IFERROR(($F$70-$F$50)/$F$50,"")</f>
         <v/>
       </c>
     </row>
     <row r="84" ht="16" customHeight="1">
       <c r="A84" s="4" t="inlineStr">
         <is>
+          <t>Likviditetsgrad, %</t>
+        </is>
+      </c>
+      <c r="B84" s="14">
+        <f>IFERROR($B$40/$B$68*100,"")</f>
+        <v/>
+      </c>
+      <c r="C84" s="14">
+        <f>IFERROR($C$40/$C$68*100,"")</f>
+        <v/>
+      </c>
+      <c r="D84" s="14">
+        <f>IFERROR($D$40/$D$68*100,"")</f>
+        <v/>
+      </c>
+      <c r="E84" s="14">
+        <f>IFERROR($E$40/$E$68*100,"")</f>
+        <v/>
+      </c>
+      <c r="F84" s="14">
+        <f>IFERROR($F$40/$F$68*100,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="85" ht="16" customHeight="1">
+      <c r="A85" s="7" t="inlineStr">
+        <is>
+          <t>Rentemarginal, %</t>
+        </is>
+      </c>
+      <c r="B85" s="13">
+        <f>IFERROR(B77-B81,"")</f>
+        <v/>
+      </c>
+      <c r="C85" s="13">
+        <f>IFERROR(C77-C81,"")</f>
+        <v/>
+      </c>
+      <c r="D85" s="13">
+        <f>IFERROR(D77-D81,"")</f>
+        <v/>
+      </c>
+      <c r="E85" s="13">
+        <f>IFERROR(E77-E81,"")</f>
+        <v/>
+      </c>
+      <c r="F85" s="13">
+        <f>IFERROR(F77-F81,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="86" ht="16" customHeight="1">
+      <c r="A86" s="4" t="inlineStr">
+        <is>
+          <t>Gældsandel, %</t>
+        </is>
+      </c>
+      <c r="B86" s="14">
+        <f>IFERROR(($B$70-$B$50)/$B$41*100,"")</f>
+        <v/>
+      </c>
+      <c r="C86" s="14">
+        <f>IFERROR(($C$70-$C$50)/$C$41*100,"")</f>
+        <v/>
+      </c>
+      <c r="D86" s="14">
+        <f>IFERROR(($D$70-$D$50)/$D$41*100,"")</f>
+        <v/>
+      </c>
+      <c r="E86" s="14">
+        <f>IFERROR(($E$70-$E$50)/$E$41*100,"")</f>
+        <v/>
+      </c>
+      <c r="F86" s="14">
+        <f>IFERROR(($F$70-$F$50)/$F$41*100,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="87" ht="16" customHeight="1">
+      <c r="A87" s="7" t="inlineStr">
+        <is>
           <t>Kapitalbindingsgrad, %</t>
         </is>
       </c>
-      <c r="B84" s="13">
-        <f>IFERROR($B$25/($B$47+$B$53)*100,"")</f>
-        <v/>
-      </c>
-      <c r="C84" s="13">
-        <f>IFERROR($C$25/($C$47+$C$53)*100,"")</f>
-        <v/>
-      </c>
-      <c r="D84" s="13">
-        <f>IFERROR($D$25/($D$47+$D$53)*100,"")</f>
-        <v/>
-      </c>
-      <c r="E84" s="13">
-        <f>IFERROR($E$25/($E$47+$E$53)*100,"")</f>
-        <v/>
-      </c>
-      <c r="F84" s="13">
-        <f>IFERROR($F$25/($F$47+$F$53)*100,"")</f>
+      <c r="B87" s="13">
+        <f>IFERROR($B$28/($B$50+$B$56)*100,"")</f>
+        <v/>
+      </c>
+      <c r="C87" s="13">
+        <f>IFERROR($C$28/($C$50+$C$56)*100,"")</f>
+        <v/>
+      </c>
+      <c r="D87" s="13">
+        <f>IFERROR($D$28/($D$50+$D$56)*100,"")</f>
+        <v/>
+      </c>
+      <c r="E87" s="13">
+        <f>IFERROR($E$28/($E$50+$E$56)*100,"")</f>
+        <v/>
+      </c>
+      <c r="F87" s="13">
+        <f>IFERROR($F$28/($F$50+$F$56)*100,"")</f>
         <v/>
       </c>
     </row>
@@ -4172,10 +4316,18 @@
         </is>
       </c>
       <c r="B3" s="16" t="n"/>
-      <c r="C3" s="16" t="n"/>
-      <c r="D3" s="16" t="n"/>
-      <c r="E3" s="16" t="n"/>
-      <c r="F3" s="16" t="n"/>
+      <c r="C3" s="16" t="n">
+        <v>96000</v>
+      </c>
+      <c r="D3" s="16" t="n">
+        <v>201000</v>
+      </c>
+      <c r="E3" s="16" t="n">
+        <v>294000</v>
+      </c>
+      <c r="F3" s="16" t="n">
+        <v>264000</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="15" t="inlineStr">
@@ -4295,10 +4447,18 @@
         </is>
       </c>
       <c r="B12" s="16" t="n"/>
-      <c r="C12" s="16" t="n"/>
-      <c r="D12" s="16" t="n"/>
-      <c r="E12" s="16" t="n"/>
-      <c r="F12" s="16" t="n"/>
+      <c r="C12" s="16" t="n">
+        <v>2814000</v>
+      </c>
+      <c r="D12" s="16" t="n">
+        <v>3734000</v>
+      </c>
+      <c r="E12" s="16" t="n">
+        <v>3013000</v>
+      </c>
+      <c r="F12" s="16" t="n">
+        <v>4447000</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
@@ -4328,16 +4488,16 @@
       </c>
       <c r="B14" s="16" t="n"/>
       <c r="C14" s="16" t="n">
-        <v>1009000</v>
+        <v>1601000</v>
       </c>
       <c r="D14" s="16" t="n">
-        <v>885000</v>
+        <v>935000</v>
       </c>
       <c r="E14" s="16" t="n">
-        <v>1053000</v>
+        <v>1120000</v>
       </c>
       <c r="F14" s="16" t="n">
-        <v>1098000</v>
+        <v>1420000</v>
       </c>
     </row>
     <row r="15">
@@ -4455,7 +4615,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F44"/>
+  <dimension ref="A1:F47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="72" customWidth="1" min="1" max="1"/>
@@ -4529,185 +4689,181 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="17" t="inlineStr">
-        <is>
-          <t>Anlægsaktiver</t>
+      <c r="A4" s="15" t="inlineStr">
+        <is>
+          <t>Kapitalandele, dattervirksomheder</t>
         </is>
       </c>
       <c r="B4" s="16" t="n"/>
-      <c r="C4" s="16" t="n">
-        <v>30226000</v>
-      </c>
-      <c r="D4" s="16" t="n">
-        <v>34045000</v>
-      </c>
-      <c r="E4" s="16" t="n">
-        <v>31512000</v>
-      </c>
-      <c r="F4" s="16" t="n">
-        <v>31991000</v>
-      </c>
+      <c r="C4" s="16" t="n"/>
+      <c r="D4" s="16" t="n"/>
+      <c r="E4" s="16" t="n"/>
+      <c r="F4" s="16" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="17" t="inlineStr">
-        <is>
-          <t>Varebeholdninger</t>
+      <c r="A5" s="15" t="inlineStr">
+        <is>
+          <t>Deposita</t>
         </is>
       </c>
       <c r="B5" s="16" t="n"/>
       <c r="C5" s="16" t="n">
+        <v>4000</v>
+      </c>
+      <c r="D5" s="16" t="n">
+        <v>11000</v>
+      </c>
+      <c r="E5" s="16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F5" s="16" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="17" t="inlineStr">
+        <is>
+          <t>Finansielle anlægsaktiver</t>
+        </is>
+      </c>
+      <c r="B6" s="16" t="n"/>
+      <c r="C6" s="16" t="n"/>
+      <c r="D6" s="16" t="n"/>
+      <c r="E6" s="16" t="n"/>
+      <c r="F6" s="16" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="17" t="inlineStr">
+        <is>
+          <t>Anlægsaktiver</t>
+        </is>
+      </c>
+      <c r="B7" s="16" t="n"/>
+      <c r="C7" s="16" t="n">
+        <v>30226000</v>
+      </c>
+      <c r="D7" s="16" t="n">
+        <v>34045000</v>
+      </c>
+      <c r="E7" s="16" t="n">
+        <v>31512000</v>
+      </c>
+      <c r="F7" s="16" t="n">
+        <v>31991000</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="17" t="inlineStr">
+        <is>
+          <t>Varebeholdninger</t>
+        </is>
+      </c>
+      <c r="B8" s="16" t="n"/>
+      <c r="C8" s="16" t="n">
         <v>889000</v>
       </c>
-      <c r="D5" s="16" t="n">
+      <c r="D8" s="16" t="n">
         <v>926000</v>
       </c>
-      <c r="E5" s="16" t="n">
+      <c r="E8" s="16" t="n">
         <v>1009000</v>
       </c>
-      <c r="F5" s="16" t="n">
+      <c r="F8" s="16" t="n">
         <v>928000</v>
       </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="15" t="inlineStr">
-        <is>
-          <t>Tilgodehavender fra salg og tjenesteydelser</t>
-        </is>
-      </c>
-      <c r="B6" s="16" t="n"/>
-      <c r="C6" s="16" t="n">
-        <v>5243000</v>
-      </c>
-      <c r="D6" s="16" t="n">
-        <v>4802000</v>
-      </c>
-      <c r="E6" s="16" t="n">
-        <v>3338000</v>
-      </c>
-      <c r="F6" s="16" t="n">
-        <v>4435000</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="15" t="inlineStr">
-        <is>
-          <t>Tilgodehavender hos tilknyttede virksomheder</t>
-        </is>
-      </c>
-      <c r="B7" s="16" t="n"/>
-      <c r="C7" s="16" t="n"/>
-      <c r="D7" s="16" t="n"/>
-      <c r="E7" s="16" t="n"/>
-      <c r="F7" s="16" t="n"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="15" t="inlineStr">
-        <is>
-          <t>Andre tilgodehavender</t>
-        </is>
-      </c>
-      <c r="B8" s="16" t="n"/>
-      <c r="C8" s="16" t="n"/>
-      <c r="D8" s="16" t="n"/>
-      <c r="E8" s="16" t="n"/>
-      <c r="F8" s="16" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="15" t="inlineStr">
         <is>
-          <t>Periodeafgrænsningsposter (aktiver)</t>
+          <t>Tilgodehavender fra salg og tjenesteydelser</t>
         </is>
       </c>
       <c r="B9" s="16" t="n"/>
       <c r="C9" s="16" t="n">
-        <v>238000</v>
+        <v>5243000</v>
       </c>
       <c r="D9" s="16" t="n">
-        <v>991000</v>
+        <v>4802000</v>
       </c>
       <c r="E9" s="16" t="n">
-        <v>909000</v>
+        <v>3338000</v>
       </c>
       <c r="F9" s="16" t="n">
-        <v>310000</v>
+        <v>4435000</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="15" t="inlineStr">
         <is>
-          <t>Udskudt skatteaktiv</t>
+          <t>Tilgodehavender hos tilknyttede virksomheder</t>
         </is>
       </c>
       <c r="B10" s="16" t="n"/>
-      <c r="C10" s="16" t="n">
-        <v>48000</v>
-      </c>
-      <c r="D10" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="E10" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" s="16" t="n">
-        <v>0</v>
-      </c>
+      <c r="C10" s="16" t="n"/>
+      <c r="D10" s="16" t="n"/>
+      <c r="E10" s="16" t="n"/>
+      <c r="F10" s="16" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="15" t="inlineStr">
         <is>
-          <t>Tilgodehavende skat hos tilknyttede virksomheder</t>
+          <t>Andre tilgodehavender</t>
         </is>
       </c>
       <c r="B11" s="16" t="n"/>
       <c r="C11" s="16" t="n"/>
-      <c r="D11" s="16" t="n"/>
-      <c r="E11" s="16" t="n"/>
-      <c r="F11" s="16" t="n"/>
+      <c r="D11" s="16" t="n">
+        <v>52000</v>
+      </c>
+      <c r="E11" s="16" t="n">
+        <v>50000</v>
+      </c>
+      <c r="F11" s="16" t="n">
+        <v>1000</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="15" t="inlineStr">
         <is>
-          <t>Kortfristede skattetilgodehavender</t>
+          <t>Periodeafgrænsningsposter (aktiver)</t>
         </is>
       </c>
       <c r="B12" s="16" t="n"/>
       <c r="C12" s="16" t="n">
-        <v>92000</v>
+        <v>238000</v>
       </c>
       <c r="D12" s="16" t="n">
-        <v>1000</v>
+        <v>991000</v>
       </c>
       <c r="E12" s="16" t="n">
-        <v>85000</v>
+        <v>909000</v>
       </c>
       <c r="F12" s="16" t="n">
-        <v>64000</v>
+        <v>310000</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="17" t="inlineStr">
-        <is>
-          <t>Tilgodehavender</t>
+      <c r="A13" s="15" t="inlineStr">
+        <is>
+          <t>Udskudt skatteaktiv</t>
         </is>
       </c>
       <c r="B13" s="16" t="n"/>
       <c r="C13" s="16" t="n">
-        <v>138000</v>
+        <v>48000</v>
       </c>
       <c r="D13" s="16" t="n">
-        <v>114000</v>
+        <v>0</v>
       </c>
       <c r="E13" s="16" t="n">
-        <v>137000</v>
+        <v>0</v>
       </c>
       <c r="F13" s="16" t="n">
-        <v>323000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>Værdipapirer</t>
+          <t>Tilgodehavende skat hos tilknyttede virksomheder</t>
         </is>
       </c>
       <c r="B14" s="16" t="n"/>
@@ -4719,125 +4875,141 @@
     <row r="15">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>Likvide beholdninger</t>
-        </is>
-      </c>
-      <c r="B15" s="16" t="n">
-        <v>15000</v>
-      </c>
+          <t>Kortfristede skattetilgodehavender</t>
+        </is>
+      </c>
+      <c r="B15" s="16" t="n"/>
       <c r="C15" s="16" t="n">
-        <v>38000</v>
+        <v>92000</v>
       </c>
       <c r="D15" s="16" t="n">
-        <v>20000</v>
+        <v>1000</v>
       </c>
       <c r="E15" s="16" t="n">
-        <v>16000</v>
+        <v>85000</v>
       </c>
       <c r="F15" s="16" t="n">
-        <v>9000</v>
+        <v>64000</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="17" t="inlineStr">
         <is>
-          <t>Omsætningsaktiver</t>
+          <t>Tilgodehavender</t>
         </is>
       </c>
       <c r="B16" s="16" t="n"/>
       <c r="C16" s="16" t="n">
-        <v>14316000</v>
+        <v>138000</v>
       </c>
       <c r="D16" s="16" t="n">
-        <v>43872000</v>
+        <v>114000</v>
       </c>
       <c r="E16" s="16" t="n">
-        <v>8329000</v>
+        <v>137000</v>
       </c>
       <c r="F16" s="16" t="n">
-        <v>10581000</v>
+        <v>323000</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="17" t="inlineStr">
-        <is>
-          <t>Aktiver</t>
+      <c r="A17" s="15" t="inlineStr">
+        <is>
+          <t>Værdipapirer</t>
         </is>
       </c>
       <c r="B17" s="16" t="n"/>
-      <c r="C17" s="16" t="n">
-        <v>44542000</v>
-      </c>
-      <c r="D17" s="16" t="n">
-        <v>77917000</v>
-      </c>
-      <c r="E17" s="16" t="n">
-        <v>39841000</v>
-      </c>
-      <c r="F17" s="16" t="n">
-        <v>42572000</v>
-      </c>
+      <c r="C17" s="16" t="n"/>
+      <c r="D17" s="16" t="n"/>
+      <c r="E17" s="16" t="n"/>
+      <c r="F17" s="16" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="15" t="inlineStr">
         <is>
-          <t>Selskabskapital</t>
-        </is>
-      </c>
-      <c r="B18" s="16" t="n"/>
+          <t>Likvide beholdninger</t>
+        </is>
+      </c>
+      <c r="B18" s="16" t="n">
+        <v>15000</v>
+      </c>
       <c r="C18" s="16" t="n">
-        <v>82000</v>
+        <v>38000</v>
       </c>
       <c r="D18" s="16" t="n">
-        <v>82000</v>
+        <v>20000</v>
       </c>
       <c r="E18" s="16" t="n">
-        <v>82000</v>
+        <v>16000</v>
       </c>
       <c r="F18" s="16" t="n">
-        <v>82000</v>
+        <v>9000</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="15" t="inlineStr">
-        <is>
-          <t>Reserve for nettoopskrivning (indre værdis metode)</t>
+      <c r="A19" s="17" t="inlineStr">
+        <is>
+          <t>Omsætningsaktiver</t>
         </is>
       </c>
       <c r="B19" s="16" t="n"/>
-      <c r="C19" s="16" t="n"/>
-      <c r="D19" s="16" t="n"/>
-      <c r="E19" s="16" t="n"/>
-      <c r="F19" s="16" t="n"/>
+      <c r="C19" s="16" t="n">
+        <v>14316000</v>
+      </c>
+      <c r="D19" s="16" t="n">
+        <v>43872000</v>
+      </c>
+      <c r="E19" s="16" t="n">
+        <v>8329000</v>
+      </c>
+      <c r="F19" s="16" t="n">
+        <v>10581000</v>
+      </c>
     </row>
     <row r="20">
-      <c r="A20" s="15" t="inlineStr">
-        <is>
-          <t>Reserve for udviklingsomkostninger</t>
+      <c r="A20" s="17" t="inlineStr">
+        <is>
+          <t>Aktiver</t>
         </is>
       </c>
       <c r="B20" s="16" t="n"/>
-      <c r="C20" s="16" t="n"/>
-      <c r="D20" s="16" t="n"/>
-      <c r="E20" s="16" t="n"/>
-      <c r="F20" s="16" t="n"/>
+      <c r="C20" s="16" t="n">
+        <v>44542000</v>
+      </c>
+      <c r="D20" s="16" t="n">
+        <v>77917000</v>
+      </c>
+      <c r="E20" s="16" t="n">
+        <v>39841000</v>
+      </c>
+      <c r="F20" s="16" t="n">
+        <v>42572000</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="15" t="inlineStr">
         <is>
-          <t>Reserve for sikringstransaktioner</t>
+          <t>Selskabskapital</t>
         </is>
       </c>
       <c r="B21" s="16" t="n"/>
-      <c r="C21" s="16" t="n"/>
-      <c r="D21" s="16" t="n"/>
-      <c r="E21" s="16" t="n"/>
-      <c r="F21" s="16" t="n"/>
+      <c r="C21" s="16" t="n">
+        <v>82000</v>
+      </c>
+      <c r="D21" s="16" t="n">
+        <v>82000</v>
+      </c>
+      <c r="E21" s="16" t="n">
+        <v>82000</v>
+      </c>
+      <c r="F21" s="16" t="n">
+        <v>82000</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="15" t="inlineStr">
         <is>
-          <t>Andre reserver</t>
+          <t>Reserve for nettoopskrivning (indre værdis metode)</t>
         </is>
       </c>
       <c r="B22" s="16" t="n"/>
@@ -4849,7 +5021,7 @@
     <row r="23">
       <c r="A23" s="15" t="inlineStr">
         <is>
-          <t>Overført resultat</t>
+          <t>Reserve for udviklingsomkostninger</t>
         </is>
       </c>
       <c r="B23" s="16" t="n"/>
@@ -4859,51 +5031,33 @@
       <c r="F23" s="16" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="17" t="inlineStr">
-        <is>
-          <t>Egenkapital i alt</t>
-        </is>
-      </c>
-      <c r="B24" s="16" t="n">
-        <v>82000</v>
-      </c>
-      <c r="C24" s="16" t="n">
-        <v>26912000</v>
-      </c>
-      <c r="D24" s="16" t="n">
-        <v>55923000</v>
-      </c>
-      <c r="E24" s="16" t="n">
-        <v>15475000</v>
-      </c>
-      <c r="F24" s="16" t="n">
-        <v>22962000</v>
-      </c>
+      <c r="A24" s="15" t="inlineStr">
+        <is>
+          <t>Reserve for sikringstransaktioner</t>
+        </is>
+      </c>
+      <c r="B24" s="16" t="n"/>
+      <c r="C24" s="16" t="n"/>
+      <c r="D24" s="16" t="n"/>
+      <c r="E24" s="16" t="n"/>
+      <c r="F24" s="16" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="17" t="inlineStr">
-        <is>
-          <t>Hensatte forpligtelser</t>
+      <c r="A25" s="15" t="inlineStr">
+        <is>
+          <t>Andre reserver</t>
         </is>
       </c>
       <c r="B25" s="16" t="n"/>
-      <c r="C25" s="16" t="n">
-        <v>223000</v>
-      </c>
-      <c r="D25" s="16" t="n">
-        <v>254000</v>
-      </c>
-      <c r="E25" s="16" t="n">
-        <v>275000</v>
-      </c>
-      <c r="F25" s="16" t="n">
-        <v>300000</v>
-      </c>
+      <c r="C25" s="16" t="n"/>
+      <c r="D25" s="16" t="n"/>
+      <c r="E25" s="16" t="n"/>
+      <c r="F25" s="16" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="15" t="inlineStr">
         <is>
-          <t>Ansvarlig lånekapital (langfristet)</t>
+          <t>Overført resultat</t>
         </is>
       </c>
       <c r="B26" s="16" t="n"/>
@@ -4913,157 +5067,159 @@
       <c r="F26" s="16" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="15" t="inlineStr">
-        <is>
-          <t>Langfristede lån</t>
-        </is>
-      </c>
-      <c r="B27" s="16" t="n"/>
-      <c r="C27" s="16" t="n"/>
-      <c r="D27" s="16" t="n"/>
-      <c r="E27" s="16" t="n"/>
-      <c r="F27" s="16" t="n"/>
+      <c r="A27" s="17" t="inlineStr">
+        <is>
+          <t>Egenkapital i alt</t>
+        </is>
+      </c>
+      <c r="B27" s="16" t="n">
+        <v>82000</v>
+      </c>
+      <c r="C27" s="16" t="n">
+        <v>26912000</v>
+      </c>
+      <c r="D27" s="16" t="n">
+        <v>55923000</v>
+      </c>
+      <c r="E27" s="16" t="n">
+        <v>15475000</v>
+      </c>
+      <c r="F27" s="16" t="n">
+        <v>22962000</v>
+      </c>
     </row>
     <row r="28">
-      <c r="A28" s="15" t="inlineStr">
-        <is>
-          <t>Leasingforpligtelser (langfristet)</t>
+      <c r="A28" s="17" t="inlineStr">
+        <is>
+          <t>Hensatte forpligtelser</t>
         </is>
       </c>
       <c r="B28" s="16" t="n"/>
       <c r="C28" s="16" t="n">
-        <v>6809000</v>
+        <v>223000</v>
       </c>
       <c r="D28" s="16" t="n">
-        <v>8598000</v>
+        <v>254000</v>
       </c>
       <c r="E28" s="16" t="n">
-        <v>5881000</v>
+        <v>275000</v>
       </c>
       <c r="F28" s="16" t="n">
-        <v>5997000</v>
+        <v>300000</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="15" t="inlineStr">
         <is>
-          <t>Anden gæld (langfristet)</t>
+          <t>Ansvarlig lånekapital (langfristet)</t>
         </is>
       </c>
       <c r="B29" s="16" t="n"/>
-      <c r="C29" s="16" t="n">
-        <v>44000</v>
-      </c>
-      <c r="D29" s="16" t="n">
-        <v>45000</v>
-      </c>
-      <c r="E29" s="16" t="n">
-        <v>416000</v>
-      </c>
-      <c r="F29" s="16" t="n">
-        <v>428000</v>
-      </c>
+      <c r="C29" s="16" t="n"/>
+      <c r="D29" s="16" t="n"/>
+      <c r="E29" s="16" t="n"/>
+      <c r="F29" s="16" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="17" t="inlineStr">
-        <is>
-          <t>Langfristede gældsforpligtelser</t>
+      <c r="A30" s="15" t="inlineStr">
+        <is>
+          <t>Langfristede lån</t>
         </is>
       </c>
       <c r="B30" s="16" t="n"/>
-      <c r="C30" s="16" t="n">
-        <v>7148000</v>
-      </c>
-      <c r="D30" s="16" t="n">
-        <v>9026000</v>
-      </c>
-      <c r="E30" s="16" t="n">
-        <v>6297000</v>
-      </c>
-      <c r="F30" s="16" t="n">
-        <v>6425000</v>
-      </c>
+      <c r="C30" s="16" t="n"/>
+      <c r="D30" s="16" t="n"/>
+      <c r="E30" s="16" t="n"/>
+      <c r="F30" s="16" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="15" t="inlineStr">
         <is>
-          <t>Ansvarlig lånekapital (kortfristet)</t>
+          <t>Leasingforpligtelser (langfristet)</t>
         </is>
       </c>
       <c r="B31" s="16" t="n"/>
-      <c r="C31" s="16" t="n"/>
-      <c r="D31" s="16" t="n"/>
-      <c r="E31" s="16" t="n"/>
-      <c r="F31" s="16" t="n"/>
+      <c r="C31" s="16" t="n">
+        <v>6809000</v>
+      </c>
+      <c r="D31" s="16" t="n">
+        <v>8598000</v>
+      </c>
+      <c r="E31" s="16" t="n">
+        <v>5881000</v>
+      </c>
+      <c r="F31" s="16" t="n">
+        <v>5997000</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="15" t="inlineStr">
         <is>
-          <t>Kortfristet del af langfristede gældsforpligtelser</t>
+          <t>Anden gæld (langfristet)</t>
         </is>
       </c>
       <c r="B32" s="16" t="n"/>
-      <c r="C32" s="16" t="n"/>
-      <c r="D32" s="16" t="n"/>
-      <c r="E32" s="16" t="n"/>
-      <c r="F32" s="16" t="n"/>
+      <c r="C32" s="16" t="n">
+        <v>44000</v>
+      </c>
+      <c r="D32" s="16" t="n">
+        <v>45000</v>
+      </c>
+      <c r="E32" s="16" t="n">
+        <v>416000</v>
+      </c>
+      <c r="F32" s="16" t="n">
+        <v>428000</v>
+      </c>
     </row>
     <row r="33">
-      <c r="A33" s="15" t="inlineStr">
-        <is>
-          <t>Kreditinstitutter</t>
+      <c r="A33" s="17" t="inlineStr">
+        <is>
+          <t>Langfristede gældsforpligtelser</t>
         </is>
       </c>
       <c r="B33" s="16" t="n"/>
-      <c r="C33" s="16" t="n"/>
-      <c r="D33" s="16" t="n"/>
-      <c r="E33" s="16" t="n"/>
-      <c r="F33" s="16" t="n"/>
+      <c r="C33" s="16" t="n">
+        <v>7148000</v>
+      </c>
+      <c r="D33" s="16" t="n">
+        <v>9026000</v>
+      </c>
+      <c r="E33" s="16" t="n">
+        <v>6297000</v>
+      </c>
+      <c r="F33" s="16" t="n">
+        <v>6425000</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="15" t="inlineStr">
         <is>
-          <t>Leasingforpligtelser (kortfristet)</t>
+          <t>Ansvarlig lånekapital (kortfristet)</t>
         </is>
       </c>
       <c r="B34" s="16" t="n"/>
-      <c r="C34" s="16" t="n">
-        <v>2782000</v>
-      </c>
-      <c r="D34" s="16" t="n">
-        <v>4322000</v>
-      </c>
-      <c r="E34" s="16" t="n">
-        <v>3803000</v>
-      </c>
-      <c r="F34" s="16" t="n">
-        <v>3063000</v>
-      </c>
+      <c r="C34" s="16" t="n"/>
+      <c r="D34" s="16" t="n"/>
+      <c r="E34" s="16" t="n"/>
+      <c r="F34" s="16" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="15" t="inlineStr">
         <is>
-          <t>Leverandører af varer og tjenesteydelser</t>
+          <t>Kortfristet del af langfristede gældsforpligtelser</t>
         </is>
       </c>
       <c r="B35" s="16" t="n"/>
-      <c r="C35" s="16" t="n">
-        <v>5189000</v>
-      </c>
-      <c r="D35" s="16" t="n">
-        <v>5494000</v>
-      </c>
-      <c r="E35" s="16" t="n">
-        <v>5337000</v>
-      </c>
-      <c r="F35" s="16" t="n">
-        <v>5816000</v>
-      </c>
+      <c r="C35" s="16" t="n"/>
+      <c r="D35" s="16" t="n"/>
+      <c r="E35" s="16" t="n"/>
+      <c r="F35" s="16" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="15" t="inlineStr">
         <is>
-          <t>Gæld til tilknyttede virksomheder</t>
+          <t>Kreditinstitutter</t>
         </is>
       </c>
       <c r="B36" s="16" t="n"/>
@@ -5075,31 +5231,47 @@
     <row r="37">
       <c r="A37" s="15" t="inlineStr">
         <is>
-          <t>Gæld til selskabsdeltagere og ledelse</t>
+          <t>Leasingforpligtelser (kortfristet)</t>
         </is>
       </c>
       <c r="B37" s="16" t="n"/>
-      <c r="C37" s="16" t="n"/>
-      <c r="D37" s="16" t="n"/>
-      <c r="E37" s="16" t="n"/>
-      <c r="F37" s="16" t="n"/>
+      <c r="C37" s="16" t="n">
+        <v>2782000</v>
+      </c>
+      <c r="D37" s="16" t="n">
+        <v>4322000</v>
+      </c>
+      <c r="E37" s="16" t="n">
+        <v>3803000</v>
+      </c>
+      <c r="F37" s="16" t="n">
+        <v>3063000</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="15" t="inlineStr">
         <is>
-          <t>Selskabsskat</t>
+          <t>Leverandører af varer og tjenesteydelser</t>
         </is>
       </c>
       <c r="B38" s="16" t="n"/>
-      <c r="C38" s="16" t="n"/>
-      <c r="D38" s="16" t="n"/>
-      <c r="E38" s="16" t="n"/>
-      <c r="F38" s="16" t="n"/>
+      <c r="C38" s="16" t="n">
+        <v>5189000</v>
+      </c>
+      <c r="D38" s="16" t="n">
+        <v>5494000</v>
+      </c>
+      <c r="E38" s="16" t="n">
+        <v>5337000</v>
+      </c>
+      <c r="F38" s="16" t="n">
+        <v>5816000</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="15" t="inlineStr">
         <is>
-          <t>Gæld til tilknyttede virksomheder vedr. selskabsskat</t>
+          <t>Gæld til tilknyttede virksomheder</t>
         </is>
       </c>
       <c r="B39" s="16" t="n"/>
@@ -5111,27 +5283,19 @@
     <row r="40">
       <c r="A40" s="15" t="inlineStr">
         <is>
-          <t>Anden gæld (kortfristet)</t>
+          <t>Gæld til selskabsdeltagere og ledelse</t>
         </is>
       </c>
       <c r="B40" s="16" t="n"/>
-      <c r="C40" s="16" t="n">
-        <v>285000</v>
-      </c>
-      <c r="D40" s="16" t="n">
-        <v>282000</v>
-      </c>
-      <c r="E40" s="16" t="n">
-        <v>705000</v>
-      </c>
-      <c r="F40" s="16" t="n">
-        <v>1365000</v>
-      </c>
+      <c r="C40" s="16" t="n"/>
+      <c r="D40" s="16" t="n"/>
+      <c r="E40" s="16" t="n"/>
+      <c r="F40" s="16" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="15" t="inlineStr">
         <is>
-          <t>Periodeafgrænsningsposter (passiver)</t>
+          <t>Selskabsskat</t>
         </is>
       </c>
       <c r="B41" s="16" t="n"/>
@@ -5141,62 +5305,106 @@
       <c r="F41" s="16" t="n"/>
     </row>
     <row r="42">
-      <c r="A42" s="17" t="inlineStr">
-        <is>
-          <t>Kortfristede gældsforpligtelser</t>
+      <c r="A42" s="15" t="inlineStr">
+        <is>
+          <t>Gæld til tilknyttede virksomheder vedr. selskabsskat</t>
         </is>
       </c>
       <c r="B42" s="16" t="n"/>
-      <c r="C42" s="16" t="n">
-        <v>10482000</v>
-      </c>
-      <c r="D42" s="16" t="n">
-        <v>12968000</v>
-      </c>
-      <c r="E42" s="16" t="n">
-        <v>18069000</v>
-      </c>
-      <c r="F42" s="16" t="n">
-        <v>13185000</v>
-      </c>
+      <c r="C42" s="16" t="n"/>
+      <c r="D42" s="16" t="n"/>
+      <c r="E42" s="16" t="n"/>
+      <c r="F42" s="16" t="n"/>
     </row>
     <row r="43">
-      <c r="A43" s="17" t="inlineStr">
-        <is>
-          <t>Gældsforpligtelser</t>
+      <c r="A43" s="15" t="inlineStr">
+        <is>
+          <t>Anden gæld (kortfristet)</t>
         </is>
       </c>
       <c r="B43" s="16" t="n"/>
       <c r="C43" s="16" t="n">
+        <v>285000</v>
+      </c>
+      <c r="D43" s="16" t="n">
+        <v>282000</v>
+      </c>
+      <c r="E43" s="16" t="n">
+        <v>705000</v>
+      </c>
+      <c r="F43" s="16" t="n">
+        <v>1365000</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="15" t="inlineStr">
+        <is>
+          <t>Periodeafgrænsningsposter (passiver)</t>
+        </is>
+      </c>
+      <c r="B44" s="16" t="n"/>
+      <c r="C44" s="16" t="n"/>
+      <c r="D44" s="16" t="n"/>
+      <c r="E44" s="16" t="n"/>
+      <c r="F44" s="16" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="17" t="inlineStr">
+        <is>
+          <t>Kortfristede gældsforpligtelser</t>
+        </is>
+      </c>
+      <c r="B45" s="16" t="n"/>
+      <c r="C45" s="16" t="n">
+        <v>10482000</v>
+      </c>
+      <c r="D45" s="16" t="n">
+        <v>12968000</v>
+      </c>
+      <c r="E45" s="16" t="n">
+        <v>18069000</v>
+      </c>
+      <c r="F45" s="16" t="n">
+        <v>13185000</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="17" t="inlineStr">
+        <is>
+          <t>Gældsforpligtelser</t>
+        </is>
+      </c>
+      <c r="B46" s="16" t="n"/>
+      <c r="C46" s="16" t="n">
         <v>17630000</v>
       </c>
-      <c r="D43" s="16" t="n">
+      <c r="D46" s="16" t="n">
         <v>21994000</v>
       </c>
-      <c r="E43" s="16" t="n">
+      <c r="E46" s="16" t="n">
         <v>24366000</v>
       </c>
-      <c r="F43" s="16" t="n">
+      <c r="F46" s="16" t="n">
         <v>19610000</v>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="17" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="17" t="inlineStr">
         <is>
           <t>Passiver</t>
         </is>
       </c>
-      <c r="B44" s="16" t="n"/>
-      <c r="C44" s="16" t="n">
+      <c r="B47" s="16" t="n"/>
+      <c r="C47" s="16" t="n">
         <v>44542000</v>
       </c>
-      <c r="D44" s="16" t="n">
+      <c r="D47" s="16" t="n">
         <v>77917000</v>
       </c>
-      <c r="E44" s="16" t="n">
+      <c r="E47" s="16" t="n">
         <v>39841000</v>
       </c>
-      <c r="F44" s="16" t="n">
+      <c r="F47" s="16" t="n">
         <v>42572000</v>
       </c>
     </row>
@@ -5574,15 +5782,15 @@
         </is>
       </c>
       <c r="B19" s="24">
-        <f>'balance_raw'!$F$4</f>
+        <f>'balance_raw'!$F$7</f>
         <v/>
       </c>
       <c r="C19" s="24">
-        <f>'balance_raw'!$E$4</f>
+        <f>'balance_raw'!$E$7</f>
         <v/>
       </c>
       <c r="D19" s="24">
-        <f>'balance_raw'!$D$4</f>
+        <f>'balance_raw'!$D$7</f>
         <v/>
       </c>
       <c r="F19" s="25" t="inlineStr">
@@ -5598,15 +5806,15 @@
         </is>
       </c>
       <c r="B20" s="24">
-        <f>'balance_raw'!$F$16</f>
+        <f>'balance_raw'!$F$19</f>
         <v/>
       </c>
       <c r="C20" s="24">
-        <f>'balance_raw'!$E$16</f>
+        <f>'balance_raw'!$E$19</f>
         <v/>
       </c>
       <c r="D20" s="24">
-        <f>'balance_raw'!$D$16</f>
+        <f>'balance_raw'!$D$19</f>
         <v/>
       </c>
       <c r="F20" s="25" t="inlineStr">
@@ -5653,15 +5861,15 @@
         </is>
       </c>
       <c r="B23" s="24">
-        <f>'balance_raw'!$F$24</f>
+        <f>'balance_raw'!$F$27</f>
         <v/>
       </c>
       <c r="C23" s="24">
-        <f>'balance_raw'!$E$24</f>
+        <f>'balance_raw'!$E$27</f>
         <v/>
       </c>
       <c r="D23" s="24">
-        <f>'balance_raw'!$D$24</f>
+        <f>'balance_raw'!$D$27</f>
         <v/>
       </c>
       <c r="F23" s="25" t="inlineStr">
@@ -5677,15 +5885,15 @@
         </is>
       </c>
       <c r="B24" s="24">
-        <f>'balance_raw'!$F$44-'balance_raw'!$F$24</f>
+        <f>'balance_raw'!$F$47-'balance_raw'!$F$27</f>
         <v/>
       </c>
       <c r="C24" s="24">
-        <f>'balance_raw'!$E$44-'balance_raw'!$E$24</f>
+        <f>'balance_raw'!$E$47-'balance_raw'!$E$27</f>
         <v/>
       </c>
       <c r="D24" s="24">
-        <f>'balance_raw'!$D$44-'balance_raw'!$D$24</f>
+        <f>'balance_raw'!$D$47-'balance_raw'!$D$27</f>
         <v/>
       </c>
       <c r="F24" s="25" t="inlineStr">
@@ -5743,15 +5951,15 @@
         </is>
       </c>
       <c r="B28" s="24">
-        <f>'balance_raw'!$F$5</f>
+        <f>'balance_raw'!$F$8</f>
         <v/>
       </c>
       <c r="C28" s="24">
-        <f>'balance_raw'!$E$5</f>
+        <f>'balance_raw'!$E$8</f>
         <v/>
       </c>
       <c r="D28" s="24">
-        <f>'balance_raw'!$D$5</f>
+        <f>'balance_raw'!$D$8</f>
         <v/>
       </c>
       <c r="F28" s="25" t="inlineStr">
@@ -5767,15 +5975,15 @@
         </is>
       </c>
       <c r="B29" s="24">
-        <f>'balance_raw'!$F$6</f>
+        <f>'balance_raw'!$F$9</f>
         <v/>
       </c>
       <c r="C29" s="24">
-        <f>'balance_raw'!$E$6</f>
+        <f>'balance_raw'!$E$9</f>
         <v/>
       </c>
       <c r="D29" s="24">
-        <f>'balance_raw'!$D$6</f>
+        <f>'balance_raw'!$D$9</f>
         <v/>
       </c>
       <c r="F29" s="25" t="inlineStr">
@@ -5791,15 +5999,15 @@
         </is>
       </c>
       <c r="B30" s="24">
-        <f>'balance_raw'!$F$42</f>
+        <f>'balance_raw'!$F$45</f>
         <v/>
       </c>
       <c r="C30" s="24">
-        <f>'balance_raw'!$E$42</f>
+        <f>'balance_raw'!$E$45</f>
         <v/>
       </c>
       <c r="D30" s="24">
-        <f>'balance_raw'!$D$42</f>
+        <f>'balance_raw'!$D$45</f>
         <v/>
       </c>
       <c r="F30" s="25" t="inlineStr">
@@ -6283,15 +6491,15 @@
         </is>
       </c>
       <c r="B61" s="29">
-        <f>IF('balance_raw'!$F$17="","—",IF(ABS(B21-'balance_raw'!$F$17)&lt;=1,"✓ OK","❌ "&amp;TEXT(B21-'balance_raw'!$F$17,"+#,##0;-#,##0")&amp;" t.kr."))</f>
+        <f>IF('balance_raw'!$F$20="","—",IF(ABS(B21-'balance_raw'!$F$20)&lt;=1,"✓ OK","❌ "&amp;TEXT(B21-'balance_raw'!$F$20,"+#,##0;-#,##0")&amp;" t.kr."))</f>
         <v/>
       </c>
       <c r="C61" s="29">
-        <f>IF('balance_raw'!$E$17="","—",IF(ABS(C21-'balance_raw'!$E$17)&lt;=1,"✓ OK","❌ "&amp;TEXT(C21-'balance_raw'!$E$17,"+#,##0;-#,##0")&amp;" t.kr."))</f>
+        <f>IF('balance_raw'!$E$20="","—",IF(ABS(C21-'balance_raw'!$E$20)&lt;=1,"✓ OK","❌ "&amp;TEXT(C21-'balance_raw'!$E$20,"+#,##0;-#,##0")&amp;" t.kr."))</f>
         <v/>
       </c>
       <c r="D61" s="29">
-        <f>IF('balance_raw'!$D$17="","—",IF(ABS(D21-'balance_raw'!$D$17)&lt;=1,"✓ OK","❌ "&amp;TEXT(D21-'balance_raw'!$D$17,"+#,##0;-#,##0")&amp;" t.kr."))</f>
+        <f>IF('balance_raw'!$D$20="","—",IF(ABS(D21-'balance_raw'!$D$20)&lt;=1,"✓ OK","❌ "&amp;TEXT(D21-'balance_raw'!$D$20,"+#,##0;-#,##0")&amp;" t.kr."))</f>
         <v/>
       </c>
       <c r="F61" s="25" t="inlineStr">
@@ -6307,15 +6515,15 @@
         </is>
       </c>
       <c r="B62" s="29">
-        <f>IF('balance_raw'!$F$44="","—",IF(ABS(B25-'balance_raw'!$F$44)&lt;=1,"✓ OK","❌ "&amp;TEXT(B25-'balance_raw'!$F$44,"+#,##0;-#,##0")&amp;" t.kr."))</f>
+        <f>IF('balance_raw'!$F$47="","—",IF(ABS(B25-'balance_raw'!$F$47)&lt;=1,"✓ OK","❌ "&amp;TEXT(B25-'balance_raw'!$F$47,"+#,##0;-#,##0")&amp;" t.kr."))</f>
         <v/>
       </c>
       <c r="C62" s="29">
-        <f>IF('balance_raw'!$E$44="","—",IF(ABS(C25-'balance_raw'!$E$44)&lt;=1,"✓ OK","❌ "&amp;TEXT(C25-'balance_raw'!$E$44,"+#,##0;-#,##0")&amp;" t.kr."))</f>
+        <f>IF('balance_raw'!$E$47="","—",IF(ABS(C25-'balance_raw'!$E$47)&lt;=1,"✓ OK","❌ "&amp;TEXT(C25-'balance_raw'!$E$47,"+#,##0;-#,##0")&amp;" t.kr."))</f>
         <v/>
       </c>
       <c r="D62" s="29">
-        <f>IF('balance_raw'!$D$44="","—",IF(ABS(D25-'balance_raw'!$D$44)&lt;=1,"✓ OK","❌ "&amp;TEXT(D25-'balance_raw'!$D$44,"+#,##0;-#,##0")&amp;" t.kr."))</f>
+        <f>IF('balance_raw'!$D$47="","—",IF(ABS(D25-'balance_raw'!$D$47)&lt;=1,"✓ OK","❌ "&amp;TEXT(D25-'balance_raw'!$D$47,"+#,##0;-#,##0")&amp;" t.kr."))</f>
         <v/>
       </c>
       <c r="F62" s="25" t="inlineStr">
@@ -6434,7 +6642,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I13"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -6510,26 +6718,26 @@
       </c>
       <c r="B3" s="34" t="inlineStr">
         <is>
-          <t>ifrs-full:CurrentDerivativeFinancialAssets</t>
+          <t>ifrs-full:NoncurrentReceivablesDueFromRelatedParties</t>
         </is>
       </c>
       <c r="C3" s="34" t="inlineStr">
         <is>
-          <t>ifrs-full:CurrentDerivativeFinancialAssets</t>
+          <t>ifrs-full:NoncurrentReceivablesDueFromRelatedParties</t>
         </is>
       </c>
       <c r="D3" s="35" t="n"/>
       <c r="E3" s="35" t="n">
-        <v>0</v>
+        <v>13000</v>
       </c>
       <c r="F3" s="35" t="n">
-        <v>52000</v>
+        <v>7000</v>
       </c>
       <c r="G3" s="35" t="n">
-        <v>50000</v>
+        <v>7000</v>
       </c>
       <c r="H3" s="35" t="n">
-        <v>1000</v>
+        <v>7000</v>
       </c>
       <c r="I3" s="36" t="inlineStr">
         <is>
@@ -6545,26 +6753,26 @@
       </c>
       <c r="B4" s="37" t="inlineStr">
         <is>
-          <t>ifrs-full:CurrentDerivativeFinancialLiabilities</t>
+          <t>ifrs-full:OtherComprehensiveIncomeNetOfTaxGainsLossesOnRemeasurementsOfDefinedBenefitPlans</t>
         </is>
       </c>
       <c r="C4" s="37" t="inlineStr">
         <is>
-          <t>ifrs-full:CurrentDerivativeFinancialLiabilities</t>
+          <t>ifrs-full:OtherComprehensiveIncomeNetOfTaxGainsLossesOnRemeasurementsOfDefinedBenefitPlans</t>
         </is>
       </c>
       <c r="D4" s="38" t="n"/>
       <c r="E4" s="38" t="n">
-        <v>45000</v>
+        <v>2000</v>
       </c>
       <c r="F4" s="38" t="n">
-        <v>5000</v>
+        <v>2000</v>
       </c>
       <c r="G4" s="38" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="H4" s="38" t="n">
-        <v>75000</v>
+        <v>0</v>
       </c>
       <c r="I4" s="39" t="inlineStr">
         <is>
@@ -6580,27 +6788,23 @@
       </c>
       <c r="B5" s="34" t="inlineStr">
         <is>
-          <t>ifrs-full:GainsLossesOnDisposalsOfNoncurrentAssets</t>
+          <t>ifrs-full:OtherInflowsOutflowsOfCashClassifiedAsFinancingActivities</t>
         </is>
       </c>
       <c r="C5" s="34" t="inlineStr">
         <is>
-          <t>ifrs-full:GainsLossesOnDisposalsOfNoncurrentAssets</t>
+          <t>ifrs-full:OtherInflowsOutflowsOfCashClassifiedAsFinancingActivities</t>
         </is>
       </c>
       <c r="D5" s="35" t="n"/>
       <c r="E5" s="35" t="n">
-        <v>96000</v>
+        <v>-125000</v>
       </c>
       <c r="F5" s="35" t="n">
-        <v>201000</v>
-      </c>
-      <c r="G5" s="35" t="n">
-        <v>294000</v>
-      </c>
-      <c r="H5" s="35" t="n">
-        <v>264000</v>
-      </c>
+        <v>83000</v>
+      </c>
+      <c r="G5" s="35" t="n"/>
+      <c r="H5" s="35" t="n"/>
       <c r="I5" s="36" t="inlineStr">
         <is>
           <t>Ingen forklaring tilgængelig.</t>
@@ -6615,265 +6819,28 @@
       </c>
       <c r="B6" s="37" t="inlineStr">
         <is>
-          <t>ifrs-full:ImpairmentLossOnFinancialAssets</t>
+          <t>ifrs-full:TradeAndOtherCurrentReceivablesDueFromRelatedParties</t>
         </is>
       </c>
       <c r="C6" s="37" t="inlineStr">
         <is>
-          <t>ifrs-full:ImpairmentLossOnFinancialAssets</t>
+          <t>ifrs-full:TradeAndOtherCurrentReceivablesDueFromRelatedParties</t>
         </is>
       </c>
       <c r="D6" s="38" t="n"/>
       <c r="E6" s="38" t="n">
-        <v>592000</v>
+        <v>7521000</v>
       </c>
       <c r="F6" s="38" t="n">
-        <v>50000</v>
+        <v>36785000</v>
       </c>
       <c r="G6" s="38" t="n">
-        <v>67000</v>
+        <v>1970000</v>
       </c>
       <c r="H6" s="38" t="n">
-        <v>322000</v>
+        <v>4222000</v>
       </c>
       <c r="I6" s="39" t="inlineStr">
-        <is>
-          <t>Ingen forklaring tilgængelig.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="30" customHeight="1">
-      <c r="A7" s="34" t="inlineStr">
-        <is>
-          <t>Øvrige (ukendt)</t>
-        </is>
-      </c>
-      <c r="B7" s="34" t="inlineStr">
-        <is>
-          <t>ifrs-full:NoncurrentDerivativeFinancialAssets</t>
-        </is>
-      </c>
-      <c r="C7" s="34" t="inlineStr">
-        <is>
-          <t>ifrs-full:NoncurrentDerivativeFinancialAssets</t>
-        </is>
-      </c>
-      <c r="D7" s="35" t="n"/>
-      <c r="E7" s="35" t="n">
-        <v>4000</v>
-      </c>
-      <c r="F7" s="35" t="n">
-        <v>11000</v>
-      </c>
-      <c r="G7" s="35" t="n">
-        <v>1000</v>
-      </c>
-      <c r="H7" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" s="36" t="inlineStr">
-        <is>
-          <t>Ingen forklaring tilgængelig.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="30" customHeight="1">
-      <c r="A8" s="37" t="inlineStr">
-        <is>
-          <t>Øvrige (ukendt)</t>
-        </is>
-      </c>
-      <c r="B8" s="37" t="inlineStr">
-        <is>
-          <t>ifrs-full:NoncurrentDerivativeFinancialLiabilities</t>
-        </is>
-      </c>
-      <c r="C8" s="37" t="inlineStr">
-        <is>
-          <t>ifrs-full:NoncurrentDerivativeFinancialLiabilities</t>
-        </is>
-      </c>
-      <c r="D8" s="38" t="n"/>
-      <c r="E8" s="38" t="n">
-        <v>1000</v>
-      </c>
-      <c r="F8" s="38" t="n">
-        <v>11000</v>
-      </c>
-      <c r="G8" s="38" t="n"/>
-      <c r="H8" s="38" t="n"/>
-      <c r="I8" s="39" t="inlineStr">
-        <is>
-          <t>Ingen forklaring tilgængelig.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="30" customHeight="1">
-      <c r="A9" s="34" t="inlineStr">
-        <is>
-          <t>Øvrige (ukendt)</t>
-        </is>
-      </c>
-      <c r="B9" s="34" t="inlineStr">
-        <is>
-          <t>ifrs-full:NoncurrentReceivablesDueFromRelatedParties</t>
-        </is>
-      </c>
-      <c r="C9" s="34" t="inlineStr">
-        <is>
-          <t>ifrs-full:NoncurrentReceivablesDueFromRelatedParties</t>
-        </is>
-      </c>
-      <c r="D9" s="35" t="n"/>
-      <c r="E9" s="35" t="n">
-        <v>13000</v>
-      </c>
-      <c r="F9" s="35" t="n">
-        <v>7000</v>
-      </c>
-      <c r="G9" s="35" t="n">
-        <v>7000</v>
-      </c>
-      <c r="H9" s="35" t="n">
-        <v>7000</v>
-      </c>
-      <c r="I9" s="36" t="inlineStr">
-        <is>
-          <t>Ingen forklaring tilgængelig.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="30" customHeight="1">
-      <c r="A10" s="37" t="inlineStr">
-        <is>
-          <t>Øvrige (ukendt)</t>
-        </is>
-      </c>
-      <c r="B10" s="37" t="inlineStr">
-        <is>
-          <t>ifrs-full:OtherComprehensiveIncomeNetOfTaxGainsLossesOnRemeasurementsOfDefinedBenefitPlans</t>
-        </is>
-      </c>
-      <c r="C10" s="37" t="inlineStr">
-        <is>
-          <t>ifrs-full:OtherComprehensiveIncomeNetOfTaxGainsLossesOnRemeasurementsOfDefinedBenefitPlans</t>
-        </is>
-      </c>
-      <c r="D10" s="38" t="n"/>
-      <c r="E10" s="38" t="n">
-        <v>2000</v>
-      </c>
-      <c r="F10" s="38" t="n">
-        <v>2000</v>
-      </c>
-      <c r="G10" s="38" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" s="38" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" s="39" t="inlineStr">
-        <is>
-          <t>Ingen forklaring tilgængelig.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="30" customHeight="1">
-      <c r="A11" s="34" t="inlineStr">
-        <is>
-          <t>Øvrige (ukendt)</t>
-        </is>
-      </c>
-      <c r="B11" s="34" t="inlineStr">
-        <is>
-          <t>ifrs-full:OtherInflowsOutflowsOfCashClassifiedAsFinancingActivities</t>
-        </is>
-      </c>
-      <c r="C11" s="34" t="inlineStr">
-        <is>
-          <t>ifrs-full:OtherInflowsOutflowsOfCashClassifiedAsFinancingActivities</t>
-        </is>
-      </c>
-      <c r="D11" s="35" t="n"/>
-      <c r="E11" s="35" t="n">
-        <v>-125000</v>
-      </c>
-      <c r="F11" s="35" t="n">
-        <v>83000</v>
-      </c>
-      <c r="G11" s="35" t="n"/>
-      <c r="H11" s="35" t="n"/>
-      <c r="I11" s="36" t="inlineStr">
-        <is>
-          <t>Ingen forklaring tilgængelig.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="30" customHeight="1">
-      <c r="A12" s="37" t="inlineStr">
-        <is>
-          <t>Øvrige (ukendt)</t>
-        </is>
-      </c>
-      <c r="B12" s="37" t="inlineStr">
-        <is>
-          <t>ifrs-full:RevenueFromDividends</t>
-        </is>
-      </c>
-      <c r="C12" s="37" t="inlineStr">
-        <is>
-          <t>ifrs-full:RevenueFromDividends</t>
-        </is>
-      </c>
-      <c r="D12" s="38" t="n"/>
-      <c r="E12" s="38" t="n">
-        <v>2814000</v>
-      </c>
-      <c r="F12" s="38" t="n">
-        <v>3734000</v>
-      </c>
-      <c r="G12" s="38" t="n">
-        <v>3013000</v>
-      </c>
-      <c r="H12" s="38" t="n">
-        <v>4447000</v>
-      </c>
-      <c r="I12" s="39" t="inlineStr">
-        <is>
-          <t>Ingen forklaring tilgængelig.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="30" customHeight="1">
-      <c r="A13" s="34" t="inlineStr">
-        <is>
-          <t>Øvrige (ukendt)</t>
-        </is>
-      </c>
-      <c r="B13" s="34" t="inlineStr">
-        <is>
-          <t>ifrs-full:TradeAndOtherCurrentReceivablesDueFromRelatedParties</t>
-        </is>
-      </c>
-      <c r="C13" s="34" t="inlineStr">
-        <is>
-          <t>ifrs-full:TradeAndOtherCurrentReceivablesDueFromRelatedParties</t>
-        </is>
-      </c>
-      <c r="D13" s="35" t="n"/>
-      <c r="E13" s="35" t="n">
-        <v>7521000</v>
-      </c>
-      <c r="F13" s="35" t="n">
-        <v>36785000</v>
-      </c>
-      <c r="G13" s="35" t="n">
-        <v>1970000</v>
-      </c>
-      <c r="H13" s="35" t="n">
-        <v>4222000</v>
-      </c>
-      <c r="I13" s="36" t="inlineStr">
         <is>
           <t>Ingen forklaring tilgængelig.</t>
         </is>

--- a/filer/32345794_apm.xlsx
+++ b/filer/32345794_apm.xlsx
@@ -648,7 +648,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Regnskabsanalyse – Resultatopgørelse &amp; Balance (t.kr.)</t>
+          <t>Regnskabsanalyse – Resultatopgørelse &amp; Balance (t.USD)</t>
         </is>
       </c>
     </row>
@@ -673,7 +673,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Resultatopgørelse t.kr.</t>
+          <t>Resultatopgørelse t.USD</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
@@ -1527,7 +1527,7 @@
     <row r="22" ht="22" customHeight="1">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>AKTIVER t.kr.</t>
+          <t>AKTIVER t.USD</t>
         </is>
       </c>
       <c r="B22" s="3" t="n">
@@ -2477,7 +2477,7 @@
     <row r="43" ht="22" customHeight="1">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>PASSIVER t.kr.</t>
+          <t>PASSIVER t.USD</t>
         </is>
       </c>
       <c r="B43" s="3" t="n">
@@ -4270,7 +4270,7 @@
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>Resultatopgørelse &amp; nøgleoplysninger (t.kr.)</t>
+          <t>Resultatopgørelse &amp; nøgleoplysninger (t.USD)</t>
         </is>
       </c>
       <c r="B1" s="3" t="n">
@@ -4629,7 +4629,7 @@
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>Balance (t.kr.)</t>
+          <t>Balance (t.USD)</t>
         </is>
       </c>
       <c r="B1" s="3" t="n">
@@ -6491,15 +6491,15 @@
         </is>
       </c>
       <c r="B61" s="29">
-        <f>IF('balance_raw'!$F$20="","—",IF(ABS(B21-'balance_raw'!$F$20)&lt;=1,"✓ OK","❌ "&amp;TEXT(B21-'balance_raw'!$F$20,"+#,##0;-#,##0")&amp;" t.kr."))</f>
+        <f>IF('balance_raw'!$F$20="","—",IF(ABS(B21-'balance_raw'!$F$20)&lt;=1,"✓ OK","❌ "&amp;TEXT(B21-'balance_raw'!$F$20,"+#,##0;-#,##0")&amp;" t.USD"))</f>
         <v/>
       </c>
       <c r="C61" s="29">
-        <f>IF('balance_raw'!$E$20="","—",IF(ABS(C21-'balance_raw'!$E$20)&lt;=1,"✓ OK","❌ "&amp;TEXT(C21-'balance_raw'!$E$20,"+#,##0;-#,##0")&amp;" t.kr."))</f>
+        <f>IF('balance_raw'!$E$20="","—",IF(ABS(C21-'balance_raw'!$E$20)&lt;=1,"✓ OK","❌ "&amp;TEXT(C21-'balance_raw'!$E$20,"+#,##0;-#,##0")&amp;" t.USD"))</f>
         <v/>
       </c>
       <c r="D61" s="29">
-        <f>IF('balance_raw'!$D$20="","—",IF(ABS(D21-'balance_raw'!$D$20)&lt;=1,"✓ OK","❌ "&amp;TEXT(D21-'balance_raw'!$D$20,"+#,##0;-#,##0")&amp;" t.kr."))</f>
+        <f>IF('balance_raw'!$D$20="","—",IF(ABS(D21-'balance_raw'!$D$20)&lt;=1,"✓ OK","❌ "&amp;TEXT(D21-'balance_raw'!$D$20,"+#,##0;-#,##0")&amp;" t.USD"))</f>
         <v/>
       </c>
       <c r="F61" s="25" t="inlineStr">
@@ -6515,15 +6515,15 @@
         </is>
       </c>
       <c r="B62" s="29">
-        <f>IF('balance_raw'!$F$47="","—",IF(ABS(B25-'balance_raw'!$F$47)&lt;=1,"✓ OK","❌ "&amp;TEXT(B25-'balance_raw'!$F$47,"+#,##0;-#,##0")&amp;" t.kr."))</f>
+        <f>IF('balance_raw'!$F$47="","—",IF(ABS(B25-'balance_raw'!$F$47)&lt;=1,"✓ OK","❌ "&amp;TEXT(B25-'balance_raw'!$F$47,"+#,##0;-#,##0")&amp;" t.USD"))</f>
         <v/>
       </c>
       <c r="C62" s="29">
-        <f>IF('balance_raw'!$E$47="","—",IF(ABS(C25-'balance_raw'!$E$47)&lt;=1,"✓ OK","❌ "&amp;TEXT(C25-'balance_raw'!$E$47,"+#,##0;-#,##0")&amp;" t.kr."))</f>
+        <f>IF('balance_raw'!$E$47="","—",IF(ABS(C25-'balance_raw'!$E$47)&lt;=1,"✓ OK","❌ "&amp;TEXT(C25-'balance_raw'!$E$47,"+#,##0;-#,##0")&amp;" t.USD"))</f>
         <v/>
       </c>
       <c r="D62" s="29">
-        <f>IF('balance_raw'!$D$47="","—",IF(ABS(D25-'balance_raw'!$D$47)&lt;=1,"✓ OK","❌ "&amp;TEXT(D25-'balance_raw'!$D$47,"+#,##0;-#,##0")&amp;" t.kr."))</f>
+        <f>IF('balance_raw'!$D$47="","—",IF(ABS(D25-'balance_raw'!$D$47)&lt;=1,"✓ OK","❌ "&amp;TEXT(D25-'balance_raw'!$D$47,"+#,##0;-#,##0")&amp;" t.USD"))</f>
         <v/>
       </c>
       <c r="F62" s="25" t="inlineStr">
@@ -6539,15 +6539,15 @@
         </is>
       </c>
       <c r="B63" s="29">
-        <f>IF(ABS(B21-B25)&lt;=1,"✓ OK","❌ "&amp;TEXT(B21-B25,"+#,##0;-#,##0")&amp;" t.kr.")</f>
+        <f>IF(ABS(B21-B25)&lt;=1,"✓ OK","❌ "&amp;TEXT(B21-B25,"+#,##0;-#,##0")&amp;" t.USD")</f>
         <v/>
       </c>
       <c r="C63" s="29">
-        <f>IF(ABS(C21-C25)&lt;=1,"✓ OK","❌ "&amp;TEXT(C21-C25,"+#,##0;-#,##0")&amp;" t.kr.")</f>
+        <f>IF(ABS(C21-C25)&lt;=1,"✓ OK","❌ "&amp;TEXT(C21-C25,"+#,##0;-#,##0")&amp;" t.USD")</f>
         <v/>
       </c>
       <c r="D63" s="29">
-        <f>IF(ABS(D21-D25)&lt;=1,"✓ OK","❌ "&amp;TEXT(D21-D25,"+#,##0;-#,##0")&amp;" t.kr.")</f>
+        <f>IF(ABS(D21-D25)&lt;=1,"✓ OK","❌ "&amp;TEXT(D21-D25,"+#,##0;-#,##0")&amp;" t.USD")</f>
         <v/>
       </c>
       <c r="F63" s="25" t="inlineStr">
@@ -6563,15 +6563,15 @@
         </is>
       </c>
       <c r="B64" s="29">
-        <f>IF('res_raw'!$F$6="","—",IF(ABS(B9-'res_raw'!$F$6)&lt;=1,"✓ OK","❌ "&amp;TEXT(B9-'res_raw'!$F$6,"+#,##0;-#,##0")&amp;" t.kr."))</f>
+        <f>IF('res_raw'!$F$6="","—",IF(ABS(B9-'res_raw'!$F$6)&lt;=1,"✓ OK","❌ "&amp;TEXT(B9-'res_raw'!$F$6,"+#,##0;-#,##0")&amp;" t.USD"))</f>
         <v/>
       </c>
       <c r="C64" s="29">
-        <f>IF('res_raw'!$E$6="","—",IF(ABS(C9-'res_raw'!$E$6)&lt;=1,"✓ OK","❌ "&amp;TEXT(C9-'res_raw'!$E$6,"+#,##0;-#,##0")&amp;" t.kr."))</f>
+        <f>IF('res_raw'!$E$6="","—",IF(ABS(C9-'res_raw'!$E$6)&lt;=1,"✓ OK","❌ "&amp;TEXT(C9-'res_raw'!$E$6,"+#,##0;-#,##0")&amp;" t.USD"))</f>
         <v/>
       </c>
       <c r="D64" s="29">
-        <f>IF('res_raw'!$D$6="","—",IF(ABS(D9-'res_raw'!$D$6)&lt;=1,"✓ OK","❌ "&amp;TEXT(D9-'res_raw'!$D$6,"+#,##0;-#,##0")&amp;" t.kr."))</f>
+        <f>IF('res_raw'!$D$6="","—",IF(ABS(D9-'res_raw'!$D$6)&lt;=1,"✓ OK","❌ "&amp;TEXT(D9-'res_raw'!$D$6,"+#,##0;-#,##0")&amp;" t.USD"))</f>
         <v/>
       </c>
       <c r="F64" s="25" t="inlineStr">
@@ -6587,15 +6587,15 @@
         </is>
       </c>
       <c r="B65" s="29">
-        <f>IF('res_raw'!$F$11="","—",IF(ABS(B13-'res_raw'!$F$11)&lt;=1,"✓ OK","❌ "&amp;TEXT(B13-'res_raw'!$F$11,"+#,##0;-#,##0")&amp;" t.kr."))</f>
+        <f>IF('res_raw'!$F$11="","—",IF(ABS(B13-'res_raw'!$F$11)&lt;=1,"✓ OK","❌ "&amp;TEXT(B13-'res_raw'!$F$11,"+#,##0;-#,##0")&amp;" t.USD"))</f>
         <v/>
       </c>
       <c r="C65" s="29">
-        <f>IF('res_raw'!$E$11="","—",IF(ABS(C13-'res_raw'!$E$11)&lt;=1,"✓ OK","❌ "&amp;TEXT(C13-'res_raw'!$E$11,"+#,##0;-#,##0")&amp;" t.kr."))</f>
+        <f>IF('res_raw'!$E$11="","—",IF(ABS(C13-'res_raw'!$E$11)&lt;=1,"✓ OK","❌ "&amp;TEXT(C13-'res_raw'!$E$11,"+#,##0;-#,##0")&amp;" t.USD"))</f>
         <v/>
       </c>
       <c r="D65" s="29">
-        <f>IF('res_raw'!$D$11="","—",IF(ABS(D13-'res_raw'!$D$11)&lt;=1,"✓ OK","❌ "&amp;TEXT(D13-'res_raw'!$D$11,"+#,##0;-#,##0")&amp;" t.kr."))</f>
+        <f>IF('res_raw'!$D$11="","—",IF(ABS(D13-'res_raw'!$D$11)&lt;=1,"✓ OK","❌ "&amp;TEXT(D13-'res_raw'!$D$11,"+#,##0;-#,##0")&amp;" t.USD"))</f>
         <v/>
       </c>
       <c r="F65" s="25" t="inlineStr">
@@ -6611,15 +6611,15 @@
         </is>
       </c>
       <c r="B66" s="29">
-        <f>IF('res_raw'!$F$16="","—",IF(ABS(B16-'res_raw'!$F$16)&lt;=1,"✓ OK","❌ "&amp;TEXT(B16-'res_raw'!$F$16,"+#,##0;-#,##0")&amp;" t.kr."))</f>
+        <f>IF('res_raw'!$F$16="","—",IF(ABS(B16-'res_raw'!$F$16)&lt;=1,"✓ OK","❌ "&amp;TEXT(B16-'res_raw'!$F$16,"+#,##0;-#,##0")&amp;" t.USD"))</f>
         <v/>
       </c>
       <c r="C66" s="29">
-        <f>IF('res_raw'!$E$16="","—",IF(ABS(C16-'res_raw'!$E$16)&lt;=1,"✓ OK","❌ "&amp;TEXT(C16-'res_raw'!$E$16,"+#,##0;-#,##0")&amp;" t.kr."))</f>
+        <f>IF('res_raw'!$E$16="","—",IF(ABS(C16-'res_raw'!$E$16)&lt;=1,"✓ OK","❌ "&amp;TEXT(C16-'res_raw'!$E$16,"+#,##0;-#,##0")&amp;" t.USD"))</f>
         <v/>
       </c>
       <c r="D66" s="29">
-        <f>IF('res_raw'!$D$16="","—",IF(ABS(D16-'res_raw'!$D$16)&lt;=1,"✓ OK","❌ "&amp;TEXT(D16-'res_raw'!$D$16,"+#,##0;-#,##0")&amp;" t.kr."))</f>
+        <f>IF('res_raw'!$D$16="","—",IF(ABS(D16-'res_raw'!$D$16)&lt;=1,"✓ OK","❌ "&amp;TEXT(D16-'res_raw'!$D$16,"+#,##0;-#,##0")&amp;" t.USD"))</f>
         <v/>
       </c>
       <c r="F66" s="25" t="inlineStr">

--- a/filer/32345794_apm.xlsx
+++ b/filer/32345794_apm.xlsx
@@ -10,8 +10,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overblik" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="res_raw" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="balance_raw" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Simpel_arts" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Noter_info" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pengestrom_raw" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Simpel_arts" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Noter_info" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -204,9 +205,9 @@
     <xf numFmtId="164" fontId="3" fillId="4" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="2" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -628,7 +629,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L87"/>
+  <dimension ref="A1:L94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="54" customWidth="1" min="1" max="1"/>
@@ -4242,6 +4243,148 @@
       </c>
       <c r="F87" s="13">
         <f>IFERROR($F$28/($F$50+$F$56)*100,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="15" t="inlineStr">
+        <is>
+          <t>PENGESTRØMSOPGØRELSE t.USD</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="16" t="inlineStr">
+        <is>
+          <t>Pengestrømme fra driftsaktivitet</t>
+        </is>
+      </c>
+      <c r="B90" s="17">
+        <f>'pengestrom_raw'!$B$2</f>
+        <v/>
+      </c>
+      <c r="C90" s="17">
+        <f>'pengestrom_raw'!$C$2</f>
+        <v/>
+      </c>
+      <c r="D90" s="17">
+        <f>'pengestrom_raw'!$D$2</f>
+        <v/>
+      </c>
+      <c r="E90" s="17">
+        <f>'pengestrom_raw'!$E$2</f>
+        <v/>
+      </c>
+      <c r="F90" s="17">
+        <f>'pengestrom_raw'!$F$2</f>
+        <v/>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="16" t="inlineStr">
+        <is>
+          <t>Pengestrømme fra investeringsaktivitet</t>
+        </is>
+      </c>
+      <c r="B91" s="17">
+        <f>'pengestrom_raw'!$B$3</f>
+        <v/>
+      </c>
+      <c r="C91" s="17">
+        <f>'pengestrom_raw'!$C$3</f>
+        <v/>
+      </c>
+      <c r="D91" s="17">
+        <f>'pengestrom_raw'!$D$3</f>
+        <v/>
+      </c>
+      <c r="E91" s="17">
+        <f>'pengestrom_raw'!$E$3</f>
+        <v/>
+      </c>
+      <c r="F91" s="17">
+        <f>'pengestrom_raw'!$F$3</f>
+        <v/>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="16" t="inlineStr">
+        <is>
+          <t>Pengestrømme fra finansieringsaktivitet</t>
+        </is>
+      </c>
+      <c r="B92" s="17">
+        <f>'pengestrom_raw'!$B$4</f>
+        <v/>
+      </c>
+      <c r="C92" s="17">
+        <f>'pengestrom_raw'!$C$4</f>
+        <v/>
+      </c>
+      <c r="D92" s="17">
+        <f>'pengestrom_raw'!$D$4</f>
+        <v/>
+      </c>
+      <c r="E92" s="17">
+        <f>'pengestrom_raw'!$E$4</f>
+        <v/>
+      </c>
+      <c r="F92" s="17">
+        <f>'pengestrom_raw'!$F$4</f>
+        <v/>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="16" t="inlineStr">
+        <is>
+          <t>Årets pengestrøm (rapporteret)</t>
+        </is>
+      </c>
+      <c r="B93" s="17">
+        <f>'pengestrom_raw'!$B$5</f>
+        <v/>
+      </c>
+      <c r="C93" s="17">
+        <f>'pengestrom_raw'!$C$5</f>
+        <v/>
+      </c>
+      <c r="D93" s="17">
+        <f>'pengestrom_raw'!$D$5</f>
+        <v/>
+      </c>
+      <c r="E93" s="17">
+        <f>'pengestrom_raw'!$E$5</f>
+        <v/>
+      </c>
+      <c r="F93" s="17">
+        <f>'pengestrom_raw'!$F$5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="16" t="inlineStr">
+        <is>
+          <t>Krydstjek: drift + inv. + fin. = årets pengestrøm</t>
+        </is>
+      </c>
+      <c r="B94">
+        <f>IF(ABS(('pengestrom_raw'!$B$2+'pengestrom_raw'!$B$3+'pengestrom_raw'!$B$4)-'pengestrom_raw'!$B$5)&lt;=2,"✓","⚠ "&amp;TEXT(('pengestrom_raw'!$B$2+'pengestrom_raw'!$B$3+'pengestrom_raw'!$B$4)-'pengestrom_raw'!$B$5,"+#,##0;-#,##0"))</f>
+        <v/>
+      </c>
+      <c r="C94">
+        <f>IF(ABS(('pengestrom_raw'!$C$2+'pengestrom_raw'!$C$3+'pengestrom_raw'!$C$4)-'pengestrom_raw'!$C$5)&lt;=2,"✓","⚠ "&amp;TEXT(('pengestrom_raw'!$C$2+'pengestrom_raw'!$C$3+'pengestrom_raw'!$C$4)-'pengestrom_raw'!$C$5,"+#,##0;-#,##0"))</f>
+        <v/>
+      </c>
+      <c r="D94">
+        <f>IF(ABS(('pengestrom_raw'!$D$2+'pengestrom_raw'!$D$3+'pengestrom_raw'!$D$4)-'pengestrom_raw'!$D$5)&lt;=2,"✓","⚠ "&amp;TEXT(('pengestrom_raw'!$D$2+'pengestrom_raw'!$D$3+'pengestrom_raw'!$D$4)-'pengestrom_raw'!$D$5,"+#,##0;-#,##0"))</f>
+        <v/>
+      </c>
+      <c r="E94">
+        <f>IF(ABS(('pengestrom_raw'!$E$2+'pengestrom_raw'!$E$3+'pengestrom_raw'!$E$4)-'pengestrom_raw'!$E$5)&lt;=2,"✓","⚠ "&amp;TEXT(('pengestrom_raw'!$E$2+'pengestrom_raw'!$E$3+'pengestrom_raw'!$E$4)-'pengestrom_raw'!$E$5,"+#,##0;-#,##0"))</f>
+        <v/>
+      </c>
+      <c r="F94">
+        <f>IF(ABS(('pengestrom_raw'!$F$2+'pengestrom_raw'!$F$3+'pengestrom_raw'!$F$4)-'pengestrom_raw'!$F$5)&lt;=2,"✓","⚠ "&amp;TEXT(('pengestrom_raw'!$F$2+'pengestrom_raw'!$F$3+'pengestrom_raw'!$F$4)-'pengestrom_raw'!$F$5,"+#,##0;-#,##0"))</f>
         <v/>
       </c>
     </row>
@@ -4290,317 +4433,317 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="15" t="inlineStr">
+      <c r="A2" s="16" t="inlineStr">
         <is>
           <t>Nettoomsætning</t>
         </is>
       </c>
-      <c r="B2" s="16" t="n"/>
-      <c r="C2" s="16" t="n">
+      <c r="B2" s="17" t="n"/>
+      <c r="C2" s="17" t="n">
         <v>40737000</v>
       </c>
-      <c r="D2" s="16" t="n">
+      <c r="D2" s="17" t="n">
         <v>62465000</v>
       </c>
-      <c r="E2" s="16" t="n">
+      <c r="E2" s="17" t="n">
         <v>34520000</v>
       </c>
-      <c r="F2" s="16" t="n">
+      <c r="F2" s="17" t="n">
         <v>39498000</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="15" t="inlineStr">
+      <c r="A3" s="16" t="inlineStr">
         <is>
           <t>Andre driftsindtægter</t>
         </is>
       </c>
-      <c r="B3" s="16" t="n"/>
-      <c r="C3" s="16" t="n">
+      <c r="B3" s="17" t="n"/>
+      <c r="C3" s="17" t="n">
         <v>96000</v>
       </c>
-      <c r="D3" s="16" t="n">
+      <c r="D3" s="17" t="n">
         <v>201000</v>
       </c>
-      <c r="E3" s="16" t="n">
+      <c r="E3" s="17" t="n">
         <v>294000</v>
       </c>
-      <c r="F3" s="16" t="n">
+      <c r="F3" s="17" t="n">
         <v>264000</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="15" t="inlineStr">
+      <c r="A4" s="16" t="inlineStr">
         <is>
           <t>Vareforbrug</t>
         </is>
       </c>
-      <c r="B4" s="16" t="n"/>
-      <c r="C4" s="16" t="n"/>
-      <c r="D4" s="16" t="n"/>
-      <c r="E4" s="16" t="n"/>
-      <c r="F4" s="16" t="n"/>
+      <c r="B4" s="17" t="n"/>
+      <c r="C4" s="17" t="n"/>
+      <c r="D4" s="17" t="n"/>
+      <c r="E4" s="17" t="n"/>
+      <c r="F4" s="17" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="15" t="inlineStr">
+      <c r="A5" s="16" t="inlineStr">
         <is>
           <t>Andre eksterne omkostninger</t>
         </is>
       </c>
-      <c r="B5" s="16" t="n"/>
-      <c r="C5" s="16" t="n">
+      <c r="B5" s="17" t="n"/>
+      <c r="C5" s="17" t="n">
         <v>24625000</v>
       </c>
-      <c r="D5" s="16" t="n">
+      <c r="D5" s="17" t="n">
         <v>31274000</v>
       </c>
-      <c r="E5" s="16" t="n"/>
-      <c r="F5" s="16" t="n"/>
+      <c r="E5" s="17" t="n"/>
+      <c r="F5" s="17" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="17" t="inlineStr">
+      <c r="A6" s="15" t="inlineStr">
         <is>
           <t>Bruttoresultat</t>
         </is>
       </c>
-      <c r="B6" s="16" t="n"/>
-      <c r="C6" s="16" t="n"/>
-      <c r="D6" s="16" t="n"/>
-      <c r="E6" s="16" t="n"/>
-      <c r="F6" s="16" t="n"/>
+      <c r="B6" s="17" t="n"/>
+      <c r="C6" s="17" t="n"/>
+      <c r="D6" s="17" t="n"/>
+      <c r="E6" s="17" t="n"/>
+      <c r="F6" s="17" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="15" t="inlineStr">
+      <c r="A7" s="16" t="inlineStr">
         <is>
           <t>Personaleomkostninger</t>
         </is>
       </c>
-      <c r="B7" s="16" t="n"/>
-      <c r="C7" s="16" t="n"/>
-      <c r="D7" s="16" t="n"/>
-      <c r="E7" s="16" t="n"/>
-      <c r="F7" s="16" t="n"/>
+      <c r="B7" s="17" t="n"/>
+      <c r="C7" s="17" t="n"/>
+      <c r="D7" s="17" t="n"/>
+      <c r="E7" s="17" t="n"/>
+      <c r="F7" s="17" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="17" t="inlineStr">
+      <c r="A8" s="15" t="inlineStr">
         <is>
           <t>Resultat før afskrivninger</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="15" t="inlineStr">
+      <c r="A9" s="16" t="inlineStr">
         <is>
           <t>Af- og nedskrivninger</t>
         </is>
       </c>
-      <c r="B9" s="16" t="n"/>
-      <c r="C9" s="16" t="n">
+      <c r="B9" s="17" t="n"/>
+      <c r="C9" s="17" t="n">
         <v>3027000</v>
       </c>
-      <c r="D9" s="16" t="n">
+      <c r="D9" s="17" t="n">
         <v>5538000</v>
       </c>
-      <c r="E9" s="16" t="n">
+      <c r="E9" s="17" t="n">
         <v>5933000</v>
       </c>
-      <c r="F9" s="16" t="n">
+      <c r="F9" s="17" t="n">
         <v>5669000</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="15" t="inlineStr">
+      <c r="A10" s="16" t="inlineStr">
         <is>
           <t>Andre driftsomkostninger</t>
         </is>
       </c>
-      <c r="B10" s="16" t="n"/>
-      <c r="C10" s="16" t="n"/>
-      <c r="D10" s="16" t="n"/>
-      <c r="E10" s="16" t="n"/>
-      <c r="F10" s="16" t="n"/>
+      <c r="B10" s="17" t="n"/>
+      <c r="C10" s="17" t="n"/>
+      <c r="D10" s="17" t="n"/>
+      <c r="E10" s="17" t="n"/>
+      <c r="F10" s="17" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="17" t="inlineStr">
+      <c r="A11" s="15" t="inlineStr">
         <is>
           <t>Resultat af primær drift</t>
         </is>
       </c>
-      <c r="B11" s="16" t="n"/>
-      <c r="C11" s="16" t="n">
+      <c r="B11" s="17" t="n"/>
+      <c r="C11" s="17" t="n">
         <v>13181000</v>
       </c>
-      <c r="D11" s="16" t="n">
+      <c r="D11" s="17" t="n">
         <v>25854000</v>
       </c>
-      <c r="E11" s="16" t="n">
+      <c r="E11" s="17" t="n">
         <v>1199000</v>
       </c>
-      <c r="F11" s="16" t="n">
+      <c r="F11" s="17" t="n">
         <v>4049000</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="15" t="inlineStr">
+      <c r="A12" s="16" t="inlineStr">
         <is>
           <t>Indtægter af kapitalandele, dattervirksomheder</t>
         </is>
       </c>
-      <c r="B12" s="16" t="n"/>
-      <c r="C12" s="16" t="n">
+      <c r="B12" s="17" t="n"/>
+      <c r="C12" s="17" t="n">
         <v>2814000</v>
       </c>
-      <c r="D12" s="16" t="n">
+      <c r="D12" s="17" t="n">
         <v>3734000</v>
       </c>
-      <c r="E12" s="16" t="n">
+      <c r="E12" s="17" t="n">
         <v>3013000</v>
       </c>
-      <c r="F12" s="16" t="n">
+      <c r="F12" s="17" t="n">
         <v>4447000</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="15" t="inlineStr">
+      <c r="A13" s="16" t="inlineStr">
         <is>
           <t>Finansielle indtægter</t>
         </is>
       </c>
-      <c r="B13" s="16" t="n"/>
-      <c r="C13" s="16" t="n">
+      <c r="B13" s="17" t="n"/>
+      <c r="C13" s="17" t="n">
         <v>73000</v>
       </c>
-      <c r="D13" s="16" t="n">
+      <c r="D13" s="17" t="n">
         <v>582000</v>
       </c>
-      <c r="E13" s="16" t="n">
+      <c r="E13" s="17" t="n">
         <v>847000</v>
       </c>
-      <c r="F13" s="16" t="n">
+      <c r="F13" s="17" t="n">
         <v>524000</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="15" t="inlineStr">
+      <c r="A14" s="16" t="inlineStr">
         <is>
           <t>Finansielle omkostninger</t>
         </is>
       </c>
-      <c r="B14" s="16" t="n"/>
-      <c r="C14" s="16" t="n">
+      <c r="B14" s="17" t="n"/>
+      <c r="C14" s="17" t="n">
         <v>1601000</v>
       </c>
-      <c r="D14" s="16" t="n">
+      <c r="D14" s="17" t="n">
         <v>935000</v>
       </c>
-      <c r="E14" s="16" t="n">
+      <c r="E14" s="17" t="n">
         <v>1120000</v>
       </c>
-      <c r="F14" s="16" t="n">
+      <c r="F14" s="17" t="n">
         <v>1420000</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="17" t="inlineStr">
+      <c r="A15" s="15" t="inlineStr">
         <is>
           <t>Finansielle poster, netto</t>
         </is>
       </c>
-      <c r="B15" s="16" t="n"/>
-      <c r="C15" s="16" t="n"/>
-      <c r="D15" s="16" t="n"/>
-      <c r="E15" s="16" t="n"/>
-      <c r="F15" s="16" t="n"/>
+      <c r="B15" s="17" t="n"/>
+      <c r="C15" s="17" t="n"/>
+      <c r="D15" s="17" t="n"/>
+      <c r="E15" s="17" t="n"/>
+      <c r="F15" s="17" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="17" t="inlineStr">
+      <c r="A16" s="15" t="inlineStr">
         <is>
           <t>Resultat før skat</t>
         </is>
       </c>
-      <c r="B16" s="16" t="n"/>
-      <c r="C16" s="16" t="n">
+      <c r="B16" s="17" t="n"/>
+      <c r="C16" s="17" t="n">
         <v>14467000</v>
       </c>
-      <c r="D16" s="16" t="n">
+      <c r="D16" s="17" t="n">
         <v>29235000</v>
       </c>
-      <c r="E16" s="16" t="n">
+      <c r="E16" s="17" t="n">
         <v>3939000</v>
       </c>
-      <c r="F16" s="16" t="n">
+      <c r="F16" s="17" t="n">
         <v>7600000</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="15" t="inlineStr">
+      <c r="A17" s="16" t="inlineStr">
         <is>
           <t>Skat af årets resultat</t>
         </is>
       </c>
-      <c r="B17" s="16" t="n"/>
-      <c r="C17" s="16" t="n">
+      <c r="B17" s="17" t="n"/>
+      <c r="C17" s="17" t="n">
         <v>59000</v>
       </c>
-      <c r="D17" s="16" t="n">
+      <c r="D17" s="17" t="n">
         <v>424000</v>
       </c>
-      <c r="E17" s="16" t="n">
+      <c r="E17" s="17" t="n">
         <v>41000</v>
       </c>
-      <c r="F17" s="16" t="n">
+      <c r="F17" s="17" t="n">
         <v>25000</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="17" t="inlineStr">
+      <c r="A18" s="15" t="inlineStr">
         <is>
           <t>Årets resultat</t>
         </is>
       </c>
-      <c r="B18" s="16" t="n"/>
-      <c r="C18" s="16" t="n">
+      <c r="B18" s="17" t="n"/>
+      <c r="C18" s="17" t="n">
         <v>14408000</v>
       </c>
-      <c r="D18" s="16" t="n">
+      <c r="D18" s="17" t="n">
         <v>28811000</v>
       </c>
-      <c r="E18" s="16" t="n">
+      <c r="E18" s="17" t="n">
         <v>3898000</v>
       </c>
-      <c r="F18" s="16" t="n">
+      <c r="F18" s="17" t="n">
         <v>7575000</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="15" t="inlineStr">
+      <c r="A19" s="16" t="inlineStr">
         <is>
           <t>Gns. antal medarbejdere</t>
         </is>
       </c>
-      <c r="B19" s="16" t="n"/>
-      <c r="C19" s="16" t="n"/>
-      <c r="D19" s="16" t="n"/>
-      <c r="E19" s="16" t="n"/>
-      <c r="F19" s="16" t="n"/>
+      <c r="B19" s="17" t="n"/>
+      <c r="C19" s="17" t="n"/>
+      <c r="D19" s="17" t="n"/>
+      <c r="E19" s="17" t="n"/>
+      <c r="F19" s="17" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="15" t="inlineStr">
+      <c r="A20" s="16" t="inlineStr">
         <is>
           <t>Investering i materielle anlægsaktiver</t>
         </is>
       </c>
-      <c r="B20" s="16" t="n"/>
-      <c r="C20" s="16" t="n">
+      <c r="B20" s="17" t="n"/>
+      <c r="C20" s="17" t="n">
         <v>1707000</v>
       </c>
-      <c r="D20" s="16" t="n">
+      <c r="D20" s="17" t="n">
         <v>1637000</v>
       </c>
-      <c r="E20" s="16" t="n">
+      <c r="E20" s="17" t="n">
         <v>1755000</v>
       </c>
-      <c r="F20" s="16" t="n">
+      <c r="F20" s="17" t="n">
         <v>2197000</v>
       </c>
     </row>
@@ -4649,762 +4792,762 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="17" t="inlineStr">
+      <c r="A2" s="15" t="inlineStr">
         <is>
           <t>Immaterielle anlægsaktiver</t>
         </is>
       </c>
-      <c r="B2" s="16" t="n"/>
-      <c r="C2" s="16" t="n">
+      <c r="B2" s="17" t="n"/>
+      <c r="C2" s="17" t="n">
         <v>1325000</v>
       </c>
-      <c r="D2" s="16" t="n">
+      <c r="D2" s="17" t="n">
         <v>1195000</v>
       </c>
-      <c r="E2" s="16" t="n">
+      <c r="E2" s="17" t="n">
         <v>851000</v>
       </c>
-      <c r="F2" s="16" t="n">
+      <c r="F2" s="17" t="n">
         <v>822000</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="17" t="inlineStr">
+      <c r="A3" s="15" t="inlineStr">
         <is>
           <t>Materielle anlægsaktiver</t>
         </is>
       </c>
-      <c r="B3" s="16" t="n"/>
-      <c r="C3" s="16" t="n">
+      <c r="B3" s="17" t="n"/>
+      <c r="C3" s="17" t="n">
         <v>13405000</v>
       </c>
-      <c r="D3" s="16" t="n">
+      <c r="D3" s="17" t="n">
         <v>13545000</v>
       </c>
-      <c r="E3" s="16" t="n">
+      <c r="E3" s="17" t="n">
         <v>14625000</v>
       </c>
-      <c r="F3" s="16" t="n">
+      <c r="F3" s="17" t="n">
         <v>15247000</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="15" t="inlineStr">
+      <c r="A4" s="16" t="inlineStr">
         <is>
           <t>Kapitalandele, dattervirksomheder</t>
         </is>
       </c>
-      <c r="B4" s="16" t="n"/>
-      <c r="C4" s="16" t="n"/>
-      <c r="D4" s="16" t="n"/>
-      <c r="E4" s="16" t="n"/>
-      <c r="F4" s="16" t="n"/>
+      <c r="B4" s="17" t="n"/>
+      <c r="C4" s="17" t="n"/>
+      <c r="D4" s="17" t="n"/>
+      <c r="E4" s="17" t="n"/>
+      <c r="F4" s="17" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="15" t="inlineStr">
+      <c r="A5" s="16" t="inlineStr">
         <is>
           <t>Deposita</t>
         </is>
       </c>
-      <c r="B5" s="16" t="n"/>
-      <c r="C5" s="16" t="n">
+      <c r="B5" s="17" t="n"/>
+      <c r="C5" s="17" t="n">
         <v>4000</v>
       </c>
-      <c r="D5" s="16" t="n">
+      <c r="D5" s="17" t="n">
         <v>11000</v>
       </c>
-      <c r="E5" s="16" t="n">
+      <c r="E5" s="17" t="n">
         <v>1000</v>
       </c>
-      <c r="F5" s="16" t="n"/>
+      <c r="F5" s="17" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="17" t="inlineStr">
+      <c r="A6" s="15" t="inlineStr">
         <is>
           <t>Finansielle anlægsaktiver</t>
         </is>
       </c>
-      <c r="B6" s="16" t="n"/>
-      <c r="C6" s="16" t="n"/>
-      <c r="D6" s="16" t="n"/>
-      <c r="E6" s="16" t="n"/>
-      <c r="F6" s="16" t="n"/>
+      <c r="B6" s="17" t="n"/>
+      <c r="C6" s="17" t="n"/>
+      <c r="D6" s="17" t="n"/>
+      <c r="E6" s="17" t="n"/>
+      <c r="F6" s="17" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="17" t="inlineStr">
+      <c r="A7" s="15" t="inlineStr">
         <is>
           <t>Anlægsaktiver</t>
         </is>
       </c>
-      <c r="B7" s="16" t="n"/>
-      <c r="C7" s="16" t="n">
+      <c r="B7" s="17" t="n"/>
+      <c r="C7" s="17" t="n">
         <v>30226000</v>
       </c>
-      <c r="D7" s="16" t="n">
+      <c r="D7" s="17" t="n">
         <v>34045000</v>
       </c>
-      <c r="E7" s="16" t="n">
+      <c r="E7" s="17" t="n">
         <v>31512000</v>
       </c>
-      <c r="F7" s="16" t="n">
+      <c r="F7" s="17" t="n">
         <v>31991000</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="17" t="inlineStr">
+      <c r="A8" s="15" t="inlineStr">
         <is>
           <t>Varebeholdninger</t>
         </is>
       </c>
-      <c r="B8" s="16" t="n"/>
-      <c r="C8" s="16" t="n">
+      <c r="B8" s="17" t="n"/>
+      <c r="C8" s="17" t="n">
         <v>889000</v>
       </c>
-      <c r="D8" s="16" t="n">
+      <c r="D8" s="17" t="n">
         <v>926000</v>
       </c>
-      <c r="E8" s="16" t="n">
+      <c r="E8" s="17" t="n">
         <v>1009000</v>
       </c>
-      <c r="F8" s="16" t="n">
+      <c r="F8" s="17" t="n">
         <v>928000</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="15" t="inlineStr">
+      <c r="A9" s="16" t="inlineStr">
         <is>
           <t>Tilgodehavender fra salg og tjenesteydelser</t>
         </is>
       </c>
-      <c r="B9" s="16" t="n"/>
-      <c r="C9" s="16" t="n">
+      <c r="B9" s="17" t="n"/>
+      <c r="C9" s="17" t="n">
         <v>5243000</v>
       </c>
-      <c r="D9" s="16" t="n">
+      <c r="D9" s="17" t="n">
         <v>4802000</v>
       </c>
-      <c r="E9" s="16" t="n">
+      <c r="E9" s="17" t="n">
         <v>3338000</v>
       </c>
-      <c r="F9" s="16" t="n">
+      <c r="F9" s="17" t="n">
         <v>4435000</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="15" t="inlineStr">
+      <c r="A10" s="16" t="inlineStr">
         <is>
           <t>Tilgodehavender hos tilknyttede virksomheder</t>
         </is>
       </c>
-      <c r="B10" s="16" t="n"/>
-      <c r="C10" s="16" t="n"/>
-      <c r="D10" s="16" t="n"/>
-      <c r="E10" s="16" t="n"/>
-      <c r="F10" s="16" t="n"/>
+      <c r="B10" s="17" t="n"/>
+      <c r="C10" s="17" t="n"/>
+      <c r="D10" s="17" t="n"/>
+      <c r="E10" s="17" t="n"/>
+      <c r="F10" s="17" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="15" t="inlineStr">
+      <c r="A11" s="16" t="inlineStr">
         <is>
           <t>Andre tilgodehavender</t>
         </is>
       </c>
-      <c r="B11" s="16" t="n"/>
-      <c r="C11" s="16" t="n"/>
-      <c r="D11" s="16" t="n">
+      <c r="B11" s="17" t="n"/>
+      <c r="C11" s="17" t="n"/>
+      <c r="D11" s="17" t="n">
         <v>52000</v>
       </c>
-      <c r="E11" s="16" t="n">
+      <c r="E11" s="17" t="n">
         <v>50000</v>
       </c>
-      <c r="F11" s="16" t="n">
+      <c r="F11" s="17" t="n">
         <v>1000</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="15" t="inlineStr">
+      <c r="A12" s="16" t="inlineStr">
         <is>
           <t>Periodeafgrænsningsposter (aktiver)</t>
         </is>
       </c>
-      <c r="B12" s="16" t="n"/>
-      <c r="C12" s="16" t="n">
+      <c r="B12" s="17" t="n"/>
+      <c r="C12" s="17" t="n">
         <v>238000</v>
       </c>
-      <c r="D12" s="16" t="n">
+      <c r="D12" s="17" t="n">
         <v>991000</v>
       </c>
-      <c r="E12" s="16" t="n">
+      <c r="E12" s="17" t="n">
         <v>909000</v>
       </c>
-      <c r="F12" s="16" t="n">
+      <c r="F12" s="17" t="n">
         <v>310000</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="15" t="inlineStr">
+      <c r="A13" s="16" t="inlineStr">
         <is>
           <t>Udskudt skatteaktiv</t>
         </is>
       </c>
-      <c r="B13" s="16" t="n"/>
-      <c r="C13" s="16" t="n">
+      <c r="B13" s="17" t="n"/>
+      <c r="C13" s="17" t="n">
         <v>48000</v>
       </c>
-      <c r="D13" s="16" t="n">
+      <c r="D13" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="E13" s="16" t="n">
+      <c r="E13" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="F13" s="16" t="n">
+      <c r="F13" s="17" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="15" t="inlineStr">
+      <c r="A14" s="16" t="inlineStr">
         <is>
           <t>Tilgodehavende skat hos tilknyttede virksomheder</t>
         </is>
       </c>
-      <c r="B14" s="16" t="n"/>
-      <c r="C14" s="16" t="n"/>
-      <c r="D14" s="16" t="n"/>
-      <c r="E14" s="16" t="n"/>
-      <c r="F14" s="16" t="n"/>
+      <c r="B14" s="17" t="n"/>
+      <c r="C14" s="17" t="n"/>
+      <c r="D14" s="17" t="n"/>
+      <c r="E14" s="17" t="n"/>
+      <c r="F14" s="17" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="15" t="inlineStr">
+      <c r="A15" s="16" t="inlineStr">
         <is>
           <t>Kortfristede skattetilgodehavender</t>
         </is>
       </c>
-      <c r="B15" s="16" t="n"/>
-      <c r="C15" s="16" t="n">
+      <c r="B15" s="17" t="n"/>
+      <c r="C15" s="17" t="n">
         <v>92000</v>
       </c>
-      <c r="D15" s="16" t="n">
+      <c r="D15" s="17" t="n">
         <v>1000</v>
       </c>
-      <c r="E15" s="16" t="n">
+      <c r="E15" s="17" t="n">
         <v>85000</v>
       </c>
-      <c r="F15" s="16" t="n">
+      <c r="F15" s="17" t="n">
         <v>64000</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="17" t="inlineStr">
+      <c r="A16" s="15" t="inlineStr">
         <is>
           <t>Tilgodehavender</t>
         </is>
       </c>
-      <c r="B16" s="16" t="n"/>
-      <c r="C16" s="16" t="n">
+      <c r="B16" s="17" t="n"/>
+      <c r="C16" s="17" t="n">
         <v>138000</v>
       </c>
-      <c r="D16" s="16" t="n">
+      <c r="D16" s="17" t="n">
         <v>114000</v>
       </c>
-      <c r="E16" s="16" t="n">
+      <c r="E16" s="17" t="n">
         <v>137000</v>
       </c>
-      <c r="F16" s="16" t="n">
+      <c r="F16" s="17" t="n">
         <v>323000</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="15" t="inlineStr">
+      <c r="A17" s="16" t="inlineStr">
         <is>
           <t>Værdipapirer</t>
         </is>
       </c>
-      <c r="B17" s="16" t="n"/>
-      <c r="C17" s="16" t="n"/>
-      <c r="D17" s="16" t="n"/>
-      <c r="E17" s="16" t="n"/>
-      <c r="F17" s="16" t="n"/>
+      <c r="B17" s="17" t="n"/>
+      <c r="C17" s="17" t="n"/>
+      <c r="D17" s="17" t="n"/>
+      <c r="E17" s="17" t="n"/>
+      <c r="F17" s="17" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="15" t="inlineStr">
+      <c r="A18" s="16" t="inlineStr">
         <is>
           <t>Likvide beholdninger</t>
         </is>
       </c>
-      <c r="B18" s="16" t="n">
+      <c r="B18" s="17" t="n">
         <v>15000</v>
       </c>
-      <c r="C18" s="16" t="n">
+      <c r="C18" s="17" t="n">
         <v>38000</v>
       </c>
-      <c r="D18" s="16" t="n">
+      <c r="D18" s="17" t="n">
         <v>20000</v>
       </c>
-      <c r="E18" s="16" t="n">
+      <c r="E18" s="17" t="n">
         <v>16000</v>
       </c>
-      <c r="F18" s="16" t="n">
+      <c r="F18" s="17" t="n">
         <v>9000</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="17" t="inlineStr">
+      <c r="A19" s="15" t="inlineStr">
         <is>
           <t>Omsætningsaktiver</t>
         </is>
       </c>
-      <c r="B19" s="16" t="n"/>
-      <c r="C19" s="16" t="n">
+      <c r="B19" s="17" t="n"/>
+      <c r="C19" s="17" t="n">
         <v>14316000</v>
       </c>
-      <c r="D19" s="16" t="n">
+      <c r="D19" s="17" t="n">
         <v>43872000</v>
       </c>
-      <c r="E19" s="16" t="n">
+      <c r="E19" s="17" t="n">
         <v>8329000</v>
       </c>
-      <c r="F19" s="16" t="n">
+      <c r="F19" s="17" t="n">
         <v>10581000</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="17" t="inlineStr">
+      <c r="A20" s="15" t="inlineStr">
         <is>
           <t>Aktiver</t>
         </is>
       </c>
-      <c r="B20" s="16" t="n"/>
-      <c r="C20" s="16" t="n">
+      <c r="B20" s="17" t="n"/>
+      <c r="C20" s="17" t="n">
         <v>44542000</v>
       </c>
-      <c r="D20" s="16" t="n">
+      <c r="D20" s="17" t="n">
         <v>77917000</v>
       </c>
-      <c r="E20" s="16" t="n">
+      <c r="E20" s="17" t="n">
         <v>39841000</v>
       </c>
-      <c r="F20" s="16" t="n">
+      <c r="F20" s="17" t="n">
         <v>42572000</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="15" t="inlineStr">
+      <c r="A21" s="16" t="inlineStr">
         <is>
           <t>Selskabskapital</t>
         </is>
       </c>
-      <c r="B21" s="16" t="n"/>
-      <c r="C21" s="16" t="n">
+      <c r="B21" s="17" t="n"/>
+      <c r="C21" s="17" t="n">
         <v>82000</v>
       </c>
-      <c r="D21" s="16" t="n">
+      <c r="D21" s="17" t="n">
         <v>82000</v>
       </c>
-      <c r="E21" s="16" t="n">
+      <c r="E21" s="17" t="n">
         <v>82000</v>
       </c>
-      <c r="F21" s="16" t="n">
+      <c r="F21" s="17" t="n">
         <v>82000</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="15" t="inlineStr">
+      <c r="A22" s="16" t="inlineStr">
         <is>
           <t>Reserve for nettoopskrivning (indre værdis metode)</t>
         </is>
       </c>
-      <c r="B22" s="16" t="n"/>
-      <c r="C22" s="16" t="n"/>
-      <c r="D22" s="16" t="n"/>
-      <c r="E22" s="16" t="n"/>
-      <c r="F22" s="16" t="n"/>
+      <c r="B22" s="17" t="n"/>
+      <c r="C22" s="17" t="n"/>
+      <c r="D22" s="17" t="n"/>
+      <c r="E22" s="17" t="n"/>
+      <c r="F22" s="17" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="15" t="inlineStr">
+      <c r="A23" s="16" t="inlineStr">
         <is>
           <t>Reserve for udviklingsomkostninger</t>
         </is>
       </c>
-      <c r="B23" s="16" t="n"/>
-      <c r="C23" s="16" t="n"/>
-      <c r="D23" s="16" t="n"/>
-      <c r="E23" s="16" t="n"/>
-      <c r="F23" s="16" t="n"/>
+      <c r="B23" s="17" t="n"/>
+      <c r="C23" s="17" t="n"/>
+      <c r="D23" s="17" t="n"/>
+      <c r="E23" s="17" t="n"/>
+      <c r="F23" s="17" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="15" t="inlineStr">
+      <c r="A24" s="16" t="inlineStr">
         <is>
           <t>Reserve for sikringstransaktioner</t>
         </is>
       </c>
-      <c r="B24" s="16" t="n"/>
-      <c r="C24" s="16" t="n"/>
-      <c r="D24" s="16" t="n"/>
-      <c r="E24" s="16" t="n"/>
-      <c r="F24" s="16" t="n"/>
+      <c r="B24" s="17" t="n"/>
+      <c r="C24" s="17" t="n"/>
+      <c r="D24" s="17" t="n"/>
+      <c r="E24" s="17" t="n"/>
+      <c r="F24" s="17" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="15" t="inlineStr">
+      <c r="A25" s="16" t="inlineStr">
         <is>
           <t>Andre reserver</t>
         </is>
       </c>
-      <c r="B25" s="16" t="n"/>
-      <c r="C25" s="16" t="n"/>
-      <c r="D25" s="16" t="n"/>
-      <c r="E25" s="16" t="n"/>
-      <c r="F25" s="16" t="n"/>
+      <c r="B25" s="17" t="n"/>
+      <c r="C25" s="17" t="n"/>
+      <c r="D25" s="17" t="n"/>
+      <c r="E25" s="17" t="n"/>
+      <c r="F25" s="17" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="15" t="inlineStr">
+      <c r="A26" s="16" t="inlineStr">
         <is>
           <t>Overført resultat</t>
         </is>
       </c>
-      <c r="B26" s="16" t="n"/>
-      <c r="C26" s="16" t="n"/>
-      <c r="D26" s="16" t="n"/>
-      <c r="E26" s="16" t="n"/>
-      <c r="F26" s="16" t="n"/>
+      <c r="B26" s="17" t="n"/>
+      <c r="C26" s="17" t="n"/>
+      <c r="D26" s="17" t="n"/>
+      <c r="E26" s="17" t="n"/>
+      <c r="F26" s="17" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="17" t="inlineStr">
+      <c r="A27" s="15" t="inlineStr">
         <is>
           <t>Egenkapital i alt</t>
         </is>
       </c>
-      <c r="B27" s="16" t="n">
+      <c r="B27" s="17" t="n">
         <v>82000</v>
       </c>
-      <c r="C27" s="16" t="n">
+      <c r="C27" s="17" t="n">
         <v>26912000</v>
       </c>
-      <c r="D27" s="16" t="n">
+      <c r="D27" s="17" t="n">
         <v>55923000</v>
       </c>
-      <c r="E27" s="16" t="n">
+      <c r="E27" s="17" t="n">
         <v>15475000</v>
       </c>
-      <c r="F27" s="16" t="n">
+      <c r="F27" s="17" t="n">
         <v>22962000</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="17" t="inlineStr">
+      <c r="A28" s="15" t="inlineStr">
         <is>
           <t>Hensatte forpligtelser</t>
         </is>
       </c>
-      <c r="B28" s="16" t="n"/>
-      <c r="C28" s="16" t="n">
+      <c r="B28" s="17" t="n"/>
+      <c r="C28" s="17" t="n">
         <v>223000</v>
       </c>
-      <c r="D28" s="16" t="n">
+      <c r="D28" s="17" t="n">
         <v>254000</v>
       </c>
-      <c r="E28" s="16" t="n">
+      <c r="E28" s="17" t="n">
         <v>275000</v>
       </c>
-      <c r="F28" s="16" t="n">
+      <c r="F28" s="17" t="n">
         <v>300000</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="15" t="inlineStr">
+      <c r="A29" s="16" t="inlineStr">
         <is>
           <t>Ansvarlig lånekapital (langfristet)</t>
         </is>
       </c>
-      <c r="B29" s="16" t="n"/>
-      <c r="C29" s="16" t="n"/>
-      <c r="D29" s="16" t="n"/>
-      <c r="E29" s="16" t="n"/>
-      <c r="F29" s="16" t="n"/>
+      <c r="B29" s="17" t="n"/>
+      <c r="C29" s="17" t="n"/>
+      <c r="D29" s="17" t="n"/>
+      <c r="E29" s="17" t="n"/>
+      <c r="F29" s="17" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="15" t="inlineStr">
+      <c r="A30" s="16" t="inlineStr">
         <is>
           <t>Langfristede lån</t>
         </is>
       </c>
-      <c r="B30" s="16" t="n"/>
-      <c r="C30" s="16" t="n"/>
-      <c r="D30" s="16" t="n"/>
-      <c r="E30" s="16" t="n"/>
-      <c r="F30" s="16" t="n"/>
+      <c r="B30" s="17" t="n"/>
+      <c r="C30" s="17" t="n"/>
+      <c r="D30" s="17" t="n"/>
+      <c r="E30" s="17" t="n"/>
+      <c r="F30" s="17" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="15" t="inlineStr">
+      <c r="A31" s="16" t="inlineStr">
         <is>
           <t>Leasingforpligtelser (langfristet)</t>
         </is>
       </c>
-      <c r="B31" s="16" t="n"/>
-      <c r="C31" s="16" t="n">
+      <c r="B31" s="17" t="n"/>
+      <c r="C31" s="17" t="n">
         <v>6809000</v>
       </c>
-      <c r="D31" s="16" t="n">
+      <c r="D31" s="17" t="n">
         <v>8598000</v>
       </c>
-      <c r="E31" s="16" t="n">
+      <c r="E31" s="17" t="n">
         <v>5881000</v>
       </c>
-      <c r="F31" s="16" t="n">
+      <c r="F31" s="17" t="n">
         <v>5997000</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="15" t="inlineStr">
+      <c r="A32" s="16" t="inlineStr">
         <is>
           <t>Anden gæld (langfristet)</t>
         </is>
       </c>
-      <c r="B32" s="16" t="n"/>
-      <c r="C32" s="16" t="n">
+      <c r="B32" s="17" t="n"/>
+      <c r="C32" s="17" t="n">
         <v>44000</v>
       </c>
-      <c r="D32" s="16" t="n">
+      <c r="D32" s="17" t="n">
         <v>45000</v>
       </c>
-      <c r="E32" s="16" t="n">
+      <c r="E32" s="17" t="n">
         <v>416000</v>
       </c>
-      <c r="F32" s="16" t="n">
+      <c r="F32" s="17" t="n">
         <v>428000</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="17" t="inlineStr">
+      <c r="A33" s="15" t="inlineStr">
         <is>
           <t>Langfristede gældsforpligtelser</t>
         </is>
       </c>
-      <c r="B33" s="16" t="n"/>
-      <c r="C33" s="16" t="n">
+      <c r="B33" s="17" t="n"/>
+      <c r="C33" s="17" t="n">
         <v>7148000</v>
       </c>
-      <c r="D33" s="16" t="n">
+      <c r="D33" s="17" t="n">
         <v>9026000</v>
       </c>
-      <c r="E33" s="16" t="n">
+      <c r="E33" s="17" t="n">
         <v>6297000</v>
       </c>
-      <c r="F33" s="16" t="n">
+      <c r="F33" s="17" t="n">
         <v>6425000</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="15" t="inlineStr">
+      <c r="A34" s="16" t="inlineStr">
         <is>
           <t>Ansvarlig lånekapital (kortfristet)</t>
         </is>
       </c>
-      <c r="B34" s="16" t="n"/>
-      <c r="C34" s="16" t="n"/>
-      <c r="D34" s="16" t="n"/>
-      <c r="E34" s="16" t="n"/>
-      <c r="F34" s="16" t="n"/>
+      <c r="B34" s="17" t="n"/>
+      <c r="C34" s="17" t="n"/>
+      <c r="D34" s="17" t="n"/>
+      <c r="E34" s="17" t="n"/>
+      <c r="F34" s="17" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="15" t="inlineStr">
+      <c r="A35" s="16" t="inlineStr">
         <is>
           <t>Kortfristet del af langfristede gældsforpligtelser</t>
         </is>
       </c>
-      <c r="B35" s="16" t="n"/>
-      <c r="C35" s="16" t="n"/>
-      <c r="D35" s="16" t="n"/>
-      <c r="E35" s="16" t="n"/>
-      <c r="F35" s="16" t="n"/>
+      <c r="B35" s="17" t="n"/>
+      <c r="C35" s="17" t="n"/>
+      <c r="D35" s="17" t="n"/>
+      <c r="E35" s="17" t="n"/>
+      <c r="F35" s="17" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="15" t="inlineStr">
+      <c r="A36" s="16" t="inlineStr">
         <is>
           <t>Kreditinstitutter</t>
         </is>
       </c>
-      <c r="B36" s="16" t="n"/>
-      <c r="C36" s="16" t="n"/>
-      <c r="D36" s="16" t="n"/>
-      <c r="E36" s="16" t="n"/>
-      <c r="F36" s="16" t="n"/>
+      <c r="B36" s="17" t="n"/>
+      <c r="C36" s="17" t="n"/>
+      <c r="D36" s="17" t="n"/>
+      <c r="E36" s="17" t="n"/>
+      <c r="F36" s="17" t="n"/>
     </row>
     <row r="37">
-      <c r="A37" s="15" t="inlineStr">
+      <c r="A37" s="16" t="inlineStr">
         <is>
           <t>Leasingforpligtelser (kortfristet)</t>
         </is>
       </c>
-      <c r="B37" s="16" t="n"/>
-      <c r="C37" s="16" t="n">
+      <c r="B37" s="17" t="n"/>
+      <c r="C37" s="17" t="n">
         <v>2782000</v>
       </c>
-      <c r="D37" s="16" t="n">
+      <c r="D37" s="17" t="n">
         <v>4322000</v>
       </c>
-      <c r="E37" s="16" t="n">
+      <c r="E37" s="17" t="n">
         <v>3803000</v>
       </c>
-      <c r="F37" s="16" t="n">
+      <c r="F37" s="17" t="n">
         <v>3063000</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="15" t="inlineStr">
+      <c r="A38" s="16" t="inlineStr">
         <is>
           <t>Leverandører af varer og tjenesteydelser</t>
         </is>
       </c>
-      <c r="B38" s="16" t="n"/>
-      <c r="C38" s="16" t="n">
+      <c r="B38" s="17" t="n"/>
+      <c r="C38" s="17" t="n">
         <v>5189000</v>
       </c>
-      <c r="D38" s="16" t="n">
+      <c r="D38" s="17" t="n">
         <v>5494000</v>
       </c>
-      <c r="E38" s="16" t="n">
+      <c r="E38" s="17" t="n">
         <v>5337000</v>
       </c>
-      <c r="F38" s="16" t="n">
+      <c r="F38" s="17" t="n">
         <v>5816000</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="15" t="inlineStr">
+      <c r="A39" s="16" t="inlineStr">
         <is>
           <t>Gæld til tilknyttede virksomheder</t>
         </is>
       </c>
-      <c r="B39" s="16" t="n"/>
-      <c r="C39" s="16" t="n"/>
-      <c r="D39" s="16" t="n"/>
-      <c r="E39" s="16" t="n"/>
-      <c r="F39" s="16" t="n"/>
+      <c r="B39" s="17" t="n"/>
+      <c r="C39" s="17" t="n"/>
+      <c r="D39" s="17" t="n"/>
+      <c r="E39" s="17" t="n"/>
+      <c r="F39" s="17" t="n"/>
     </row>
     <row r="40">
-      <c r="A40" s="15" t="inlineStr">
+      <c r="A40" s="16" t="inlineStr">
         <is>
           <t>Gæld til selskabsdeltagere og ledelse</t>
         </is>
       </c>
-      <c r="B40" s="16" t="n"/>
-      <c r="C40" s="16" t="n"/>
-      <c r="D40" s="16" t="n"/>
-      <c r="E40" s="16" t="n"/>
-      <c r="F40" s="16" t="n"/>
+      <c r="B40" s="17" t="n"/>
+      <c r="C40" s="17" t="n"/>
+      <c r="D40" s="17" t="n"/>
+      <c r="E40" s="17" t="n"/>
+      <c r="F40" s="17" t="n"/>
     </row>
     <row r="41">
-      <c r="A41" s="15" t="inlineStr">
+      <c r="A41" s="16" t="inlineStr">
         <is>
           <t>Selskabsskat</t>
         </is>
       </c>
-      <c r="B41" s="16" t="n"/>
-      <c r="C41" s="16" t="n"/>
-      <c r="D41" s="16" t="n"/>
-      <c r="E41" s="16" t="n"/>
-      <c r="F41" s="16" t="n"/>
+      <c r="B41" s="17" t="n"/>
+      <c r="C41" s="17" t="n"/>
+      <c r="D41" s="17" t="n"/>
+      <c r="E41" s="17" t="n"/>
+      <c r="F41" s="17" t="n"/>
     </row>
     <row r="42">
-      <c r="A42" s="15" t="inlineStr">
+      <c r="A42" s="16" t="inlineStr">
         <is>
           <t>Gæld til tilknyttede virksomheder vedr. selskabsskat</t>
         </is>
       </c>
-      <c r="B42" s="16" t="n"/>
-      <c r="C42" s="16" t="n"/>
-      <c r="D42" s="16" t="n"/>
-      <c r="E42" s="16" t="n"/>
-      <c r="F42" s="16" t="n"/>
+      <c r="B42" s="17" t="n"/>
+      <c r="C42" s="17" t="n"/>
+      <c r="D42" s="17" t="n"/>
+      <c r="E42" s="17" t="n"/>
+      <c r="F42" s="17" t="n"/>
     </row>
     <row r="43">
-      <c r="A43" s="15" t="inlineStr">
+      <c r="A43" s="16" t="inlineStr">
         <is>
           <t>Anden gæld (kortfristet)</t>
         </is>
       </c>
-      <c r="B43" s="16" t="n"/>
-      <c r="C43" s="16" t="n">
+      <c r="B43" s="17" t="n"/>
+      <c r="C43" s="17" t="n">
         <v>285000</v>
       </c>
-      <c r="D43" s="16" t="n">
+      <c r="D43" s="17" t="n">
         <v>282000</v>
       </c>
-      <c r="E43" s="16" t="n">
+      <c r="E43" s="17" t="n">
         <v>705000</v>
       </c>
-      <c r="F43" s="16" t="n">
+      <c r="F43" s="17" t="n">
         <v>1365000</v>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="15" t="inlineStr">
+      <c r="A44" s="16" t="inlineStr">
         <is>
           <t>Periodeafgrænsningsposter (passiver)</t>
         </is>
       </c>
-      <c r="B44" s="16" t="n"/>
-      <c r="C44" s="16" t="n"/>
-      <c r="D44" s="16" t="n"/>
-      <c r="E44" s="16" t="n"/>
-      <c r="F44" s="16" t="n"/>
+      <c r="B44" s="17" t="n"/>
+      <c r="C44" s="17" t="n"/>
+      <c r="D44" s="17" t="n"/>
+      <c r="E44" s="17" t="n"/>
+      <c r="F44" s="17" t="n"/>
     </row>
     <row r="45">
-      <c r="A45" s="17" t="inlineStr">
+      <c r="A45" s="15" t="inlineStr">
         <is>
           <t>Kortfristede gældsforpligtelser</t>
         </is>
       </c>
-      <c r="B45" s="16" t="n"/>
-      <c r="C45" s="16" t="n">
+      <c r="B45" s="17" t="n"/>
+      <c r="C45" s="17" t="n">
         <v>10482000</v>
       </c>
-      <c r="D45" s="16" t="n">
+      <c r="D45" s="17" t="n">
         <v>12968000</v>
       </c>
-      <c r="E45" s="16" t="n">
+      <c r="E45" s="17" t="n">
         <v>18069000</v>
       </c>
-      <c r="F45" s="16" t="n">
+      <c r="F45" s="17" t="n">
         <v>13185000</v>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="17" t="inlineStr">
+      <c r="A46" s="15" t="inlineStr">
         <is>
           <t>Gældsforpligtelser</t>
         </is>
       </c>
-      <c r="B46" s="16" t="n"/>
-      <c r="C46" s="16" t="n">
+      <c r="B46" s="17" t="n"/>
+      <c r="C46" s="17" t="n">
         <v>17630000</v>
       </c>
-      <c r="D46" s="16" t="n">
+      <c r="D46" s="17" t="n">
         <v>21994000</v>
       </c>
-      <c r="E46" s="16" t="n">
+      <c r="E46" s="17" t="n">
         <v>24366000</v>
       </c>
-      <c r="F46" s="16" t="n">
+      <c r="F46" s="17" t="n">
         <v>19610000</v>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="17" t="inlineStr">
+      <c r="A47" s="15" t="inlineStr">
         <is>
           <t>Passiver</t>
         </is>
       </c>
-      <c r="B47" s="16" t="n"/>
-      <c r="C47" s="16" t="n">
+      <c r="B47" s="17" t="n"/>
+      <c r="C47" s="17" t="n">
         <v>44542000</v>
       </c>
-      <c r="D47" s="16" t="n">
+      <c r="D47" s="17" t="n">
         <v>77917000</v>
       </c>
-      <c r="E47" s="16" t="n">
+      <c r="E47" s="17" t="n">
         <v>39841000</v>
       </c>
-      <c r="F47" s="16" t="n">
+      <c r="F47" s="17" t="n">
         <v>42572000</v>
       </c>
     </row>
@@ -5414,6 +5557,122 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="72" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>Pengestrømsopgørelse (t.USD)</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="n">
+        <v>2020</v>
+      </c>
+      <c r="C1" s="3" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D1" s="3" t="n">
+        <v>2022</v>
+      </c>
+      <c r="E1" s="3" t="n">
+        <v>2023</v>
+      </c>
+      <c r="F1" s="3" t="n">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="16" t="inlineStr">
+        <is>
+          <t>Pengestrømme fra driftsaktivitet</t>
+        </is>
+      </c>
+      <c r="B2" s="17" t="n"/>
+      <c r="C2" s="17" t="n">
+        <v>15107000</v>
+      </c>
+      <c r="D2" s="17" t="n">
+        <v>30917000</v>
+      </c>
+      <c r="E2" s="17" t="n">
+        <v>9091000</v>
+      </c>
+      <c r="F2" s="17" t="n">
+        <v>7735000</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="16" t="inlineStr">
+        <is>
+          <t>Pengestrømme fra investeringsaktivitet</t>
+        </is>
+      </c>
+      <c r="B3" s="17" t="n"/>
+      <c r="C3" s="17" t="n">
+        <v>363000</v>
+      </c>
+      <c r="D3" s="17" t="n">
+        <v>-26254000</v>
+      </c>
+      <c r="E3" s="17" t="n">
+        <v>38054000</v>
+      </c>
+      <c r="F3" s="17" t="n">
+        <v>-2461000</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="16" t="inlineStr">
+        <is>
+          <t>Pengestrømme fra finansieringsaktivitet</t>
+        </is>
+      </c>
+      <c r="B4" s="17" t="n"/>
+      <c r="C4" s="17" t="n">
+        <v>-15451000</v>
+      </c>
+      <c r="D4" s="17" t="n">
+        <v>-4610000</v>
+      </c>
+      <c r="E4" s="17" t="n">
+        <v>-46999000</v>
+      </c>
+      <c r="F4" s="17" t="n">
+        <v>-5334000</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="16" t="inlineStr">
+        <is>
+          <t>Årets pengestrøm</t>
+        </is>
+      </c>
+      <c r="B5" s="17" t="n"/>
+      <c r="C5" s="17" t="n"/>
+      <c r="D5" s="17" t="n"/>
+      <c r="E5" s="17" t="n"/>
+      <c r="F5" s="17" t="n"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6636,7 +6895,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
